--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -1,16 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris WebOffice" lastEdited="7" lowestEdited="4" rupBuild=""/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="36" windowWidth="25752" windowHeight="11592"/>
   </bookViews>
   <sheets>
     <sheet name="UNIT" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -32,9 +36,6 @@
     <t>AttackSpeed</t>
   </si>
   <si>
-    <t>MovementSpeed</t>
-  </si>
-  <si>
     <t>DeployCost</t>
   </si>
   <si>
@@ -93,361 +94,74 @@
   </si>
   <si>
     <t>level</t>
+  </si>
+  <si>
+    <t>UpgradeCost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="1"/>
-    </font>
-    <font>
-      <sz val="8.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF000000"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="10"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="11"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="11"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color rgb="FFFF0000"/>
-    </font>
-    <font>
-      <sz val="18.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF3F3F76"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF3F3F3F"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFA7D00"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFA7D00"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="1"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF006100"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF9C0006"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF9C6500"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="0"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FF000000"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -462,327 +176,63 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FFACCCEA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399980"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
-    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
-    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
-    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
-    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
-    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
-    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
-    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
-    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
-    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
-    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
-    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
-    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
-    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
-    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
-    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
-    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
-    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
-    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
-    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
-    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
-    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
-    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
-    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
-    <cellStyle name="경고문" xfId="9" builtinId="11"/>
-    <cellStyle name="계산" xfId="17" builtinId="22"/>
-    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
-    <cellStyle name="메모" xfId="8" builtinId="10"/>
-    <cellStyle name="백분율" xfId="3" builtinId="5"/>
-    <cellStyle name="보통" xfId="23" builtinId="28"/>
-    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
-    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
-    <cellStyle name="열어본 하이퍼링크" xfId="7" builtinId="9" hidden="1"/>
-    <cellStyle name="요약" xfId="20" builtinId="25"/>
-    <cellStyle name="입력" xfId="15" builtinId="20"/>
-    <cellStyle name="제목" xfId="10" builtinId="15"/>
-    <cellStyle name="제목1" xfId="11" builtinId="16"/>
-    <cellStyle name="제목2" xfId="12" builtinId="17"/>
-    <cellStyle name="제목3" xfId="13" builtinId="18"/>
-    <cellStyle name="제목4" xfId="14" builtinId="19"/>
-    <cellStyle name="좋음" xfId="21" builtinId="26"/>
-    <cellStyle name="출력" xfId="16" builtinId="21"/>
-    <cellStyle name="통화" xfId="2" builtinId="4"/>
-    <cellStyle name="통화[0]" xfId="5" builtinId="7"/>
+  <cellStyles count="3">
+    <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="6" builtinId="8" hidden="1"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1072,22 +522,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultRowHeight="16.500000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="2" max="2" style="1" width="13.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="3" max="3" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="4" max="4" style="1" width="12.50500011" customWidth="1" outlineLevel="0"/>
-    <col min="5" max="5" style="1" width="13.25500011" customWidth="1" outlineLevel="0"/>
-    <col min="6" max="6" style="1" width="13.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="7" max="7" style="1" width="17.12999916" customWidth="1" outlineLevel="0"/>
-    <col min="8" max="8" style="1" width="12.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="9" max="16384" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.09765625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.3984375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.3984375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1098,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -1107,15 +559,19 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>50</v>
@@ -1133,15 +589,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>1002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -1152,19 +608,19 @@
       <c r="F3" s="1">
         <v>1</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>1003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -1175,16 +631,16 @@
       <c r="F4" s="1">
         <v>1</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>1004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1">
         <v>50</v>
@@ -1202,15 +658,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>1005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -1221,19 +677,19 @@
       <c r="F6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>1006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -1244,16 +700,16 @@
       <c r="F7" s="1">
         <v>1</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>1007</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>50</v>
@@ -1271,15 +727,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>1008</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -1290,19 +746,19 @@
       <c r="F9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>1009</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -1313,19 +769,19 @@
       <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>1010</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -1334,21 +790,21 @@
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>1011</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1">
-        <v>110</v>
+        <v>800</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -1357,21 +813,21 @@
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>1012</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1">
-        <v>120</v>
+        <v>1200</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -1380,21 +836,21 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>1013</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -1409,15 +865,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>1014</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="1">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -1428,19 +884,19 @@
       <c r="F15" s="1">
         <v>1</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>1015</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" s="1">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -1451,19 +907,19 @@
       <c r="F16" s="1">
         <v>1</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>1016</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="1">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -1478,15 +934,15 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>1017</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" s="1">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -1497,19 +953,19 @@
       <c r="F18" s="1">
         <v>1</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>130</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>1018</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -1520,13 +976,13 @@
       <c r="F19" s="1">
         <v>1</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>140</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="Polaris WebOffice" lastEdited="4" lowestEdited="4" rupBuild=""/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="UNIT" sheetId="1" r:id="rId1"/>
+    <sheet name="TowerData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>key</t>
   </si>
@@ -113,50 +114,355 @@
   </si>
   <si>
     <t>3_dark_spirit</t>
-  </si>
-  <si>
-    <t>FALSE</t>
-  </si>
-  <si>
-    <t>TRUE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
-    <font>
-      <sz val="11"/>
+  <numFmts count="0"/>
+  <fonts count="21">
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="10"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="11"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F76"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F3F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -171,23 +477,321 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFACCCEA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399980"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
+    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
+    <cellStyle name="경고문" xfId="9" builtinId="11"/>
+    <cellStyle name="계산" xfId="17" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
+    <cellStyle name="메모" xfId="8" builtinId="10"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="보통" xfId="23" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
+    <cellStyle name="열어본 하이퍼링크" xfId="7" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="20" builtinId="25"/>
+    <cellStyle name="입력" xfId="15" builtinId="20"/>
+    <cellStyle name="제목" xfId="10" builtinId="15"/>
+    <cellStyle name="제목1" xfId="11" builtinId="16"/>
+    <cellStyle name="제목2" xfId="12" builtinId="17"/>
+    <cellStyle name="제목3" xfId="13" builtinId="18"/>
+    <cellStyle name="제목4" xfId="14" builtinId="19"/>
+    <cellStyle name="좋음" xfId="21" builtinId="26"/>
+    <cellStyle name="출력" xfId="16" builtinId="21"/>
+    <cellStyle name="통화" xfId="2" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="하이퍼링크" xfId="6" builtinId="8" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -477,7 +1081,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.500000"/>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
@@ -527,798 +1131,800 @@
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2">
+      <c r="A2" s="0">
         <v>1001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>50</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
+      <c r="D2" s="0">
+        <v>1</v>
+      </c>
+      <c r="E2" s="0">
         <v>5</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="F2" s="0">
+        <v>1</v>
+      </c>
+      <c r="G2" s="0">
         <v>20</v>
       </c>
-      <c r="I2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
+      <c r="I2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" s="0">
+        <v>0</v>
+      </c>
+      <c r="M2" s="0">
+        <v>0</v>
+      </c>
+      <c r="N2" s="0">
+        <v>1</v>
+      </c>
+      <c r="O2" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3">
+      <c r="A3" s="0">
         <v>1002</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <v>100</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0">
         <v>2</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="0">
         <v>10</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
+      <c r="F3" s="0">
+        <v>1</v>
+      </c>
+      <c r="H3" s="0">
         <v>30</v>
       </c>
-      <c r="I3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
+      <c r="I3" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="0">
+        <v>0</v>
+      </c>
+      <c r="M3" s="0">
+        <v>0</v>
+      </c>
+      <c r="N3" s="0">
+        <v>1</v>
+      </c>
+      <c r="O3" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4">
+      <c r="A4" s="0">
         <v>1003</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0">
         <v>150</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0">
         <v>3</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="0">
         <v>20</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="F4" s="0">
+        <v>1</v>
+      </c>
+      <c r="H4" s="0">
         <v>40</v>
       </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
+      <c r="I4" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="0">
+        <v>0</v>
+      </c>
+      <c r="M4" s="0">
+        <v>0</v>
+      </c>
+      <c r="N4" s="0">
+        <v>1</v>
+      </c>
+      <c r="O4" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5">
+      <c r="A5" s="0">
         <v>1004</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0">
         <v>50</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
+      <c r="D5" s="0">
+        <v>1</v>
+      </c>
+      <c r="E5" s="0">
         <v>5</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="0">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0">
         <v>30</v>
       </c>
-      <c r="I5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5">
-        <v>0.5</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
+      <c r="I5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="0">
+        <v>0</v>
+      </c>
+      <c r="M5" s="0">
+        <v>0</v>
+      </c>
+      <c r="N5" s="0">
+        <v>1</v>
+      </c>
+      <c r="O5" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6">
+      <c r="A6" s="0">
         <v>1005</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0">
         <v>100</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0">
         <v>2</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="0">
         <v>10</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="H6">
+      <c r="F6" s="0">
+        <v>1</v>
+      </c>
+      <c r="H6" s="0">
         <v>40</v>
       </c>
-      <c r="I6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6">
-        <v>0.5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
+      <c r="I6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="0">
+        <v>0</v>
+      </c>
+      <c r="M6" s="0">
+        <v>0</v>
+      </c>
+      <c r="N6" s="0">
+        <v>1</v>
+      </c>
+      <c r="O6" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7">
+      <c r="A7" s="0">
         <v>1006</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0">
         <v>150</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="0">
         <v>3</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="0">
         <v>20</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="H7">
+      <c r="F7" s="0">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0">
         <v>50</v>
       </c>
-      <c r="I7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7">
-        <v>0.5</v>
-      </c>
-      <c r="M7">
-        <v>2</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
+      <c r="I7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="0">
+        <v>0</v>
+      </c>
+      <c r="M7" s="0">
+        <v>0</v>
+      </c>
+      <c r="N7" s="0">
+        <v>1</v>
+      </c>
+      <c r="O7" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8">
+      <c r="A8" s="0">
         <v>1007</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0">
         <v>50</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
+      <c r="D8" s="0">
+        <v>1</v>
+      </c>
+      <c r="E8" s="0">
         <v>5</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
+      <c r="F8" s="0">
+        <v>1</v>
+      </c>
+      <c r="G8" s="0">
         <v>50</v>
       </c>
-      <c r="I8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" t="s">
-        <v>33</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
+      <c r="I8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="0">
+        <v>0</v>
+      </c>
+      <c r="M8" s="0">
+        <v>0</v>
+      </c>
+      <c r="N8" s="0">
+        <v>1</v>
+      </c>
+      <c r="O8" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9">
+      <c r="A9" s="0">
         <v>1008</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0">
         <v>100</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="0">
         <v>2</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="0">
         <v>10</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="H9">
+      <c r="F9" s="0">
+        <v>1</v>
+      </c>
+      <c r="H9" s="0">
         <v>60</v>
       </c>
-      <c r="I9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" t="s">
-        <v>33</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9">
+      <c r="I9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="0">
+        <v>0</v>
+      </c>
+      <c r="M9" s="0">
+        <v>0</v>
+      </c>
+      <c r="N9" s="0">
+        <v>1</v>
+      </c>
+      <c r="O9" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10">
+      <c r="A10" s="0">
         <v>1009</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="0">
         <v>150</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="0">
         <v>3</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="0">
         <v>20</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="H10">
+      <c r="F10" s="0">
+        <v>1</v>
+      </c>
+      <c r="H10" s="0">
         <v>70</v>
       </c>
-      <c r="I10" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K10" t="s">
-        <v>33</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="O10">
+      <c r="I10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="0">
+        <v>0</v>
+      </c>
+      <c r="M10" s="0">
+        <v>0</v>
+      </c>
+      <c r="N10" s="0">
+        <v>1</v>
+      </c>
+      <c r="O10" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11">
+      <c r="A11" s="0">
         <v>1010</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="0">
         <v>400</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
+      <c r="D11" s="0">
+        <v>1</v>
+      </c>
+      <c r="E11" s="0">
+        <v>0</v>
+      </c>
+      <c r="F11" s="0">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0">
         <v>75</v>
       </c>
-      <c r="I11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" t="s">
-        <v>33</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>3</v>
-      </c>
-      <c r="O11">
+      <c r="I11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="0">
+        <v>0</v>
+      </c>
+      <c r="M11" s="0">
+        <v>0</v>
+      </c>
+      <c r="N11" s="0">
+        <v>1</v>
+      </c>
+      <c r="O11" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12">
+      <c r="A12" s="0">
         <v>1011</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="0">
         <v>800</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="0">
         <v>2</v>
       </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="H12">
+      <c r="E12" s="0">
+        <v>0</v>
+      </c>
+      <c r="F12" s="0">
+        <v>0</v>
+      </c>
+      <c r="H12" s="0">
         <v>80</v>
       </c>
-      <c r="I12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K12" t="s">
-        <v>33</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>3</v>
-      </c>
-      <c r="O12">
+      <c r="I12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="0">
+        <v>0</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0</v>
+      </c>
+      <c r="N12" s="0">
+        <v>1</v>
+      </c>
+      <c r="O12" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13">
+      <c r="A13" s="0">
         <v>1012</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="0">
         <v>1200</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="0">
         <v>3</v>
       </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="H13">
+      <c r="E13" s="0">
+        <v>0</v>
+      </c>
+      <c r="F13" s="0">
+        <v>0</v>
+      </c>
+      <c r="H13" s="0">
         <v>95</v>
       </c>
-      <c r="I13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" t="s">
-        <v>33</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>3</v>
-      </c>
-      <c r="O13">
+      <c r="I13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="0">
+        <v>0</v>
+      </c>
+      <c r="M13" s="0">
+        <v>0</v>
+      </c>
+      <c r="N13" s="0">
+        <v>1</v>
+      </c>
+      <c r="O13" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14">
+      <c r="A14" s="0">
         <v>1013</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="0">
         <v>100</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
+      <c r="D14" s="0">
+        <v>1</v>
+      </c>
+      <c r="E14" s="0">
         <v>30</v>
       </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
+      <c r="F14" s="0">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0">
         <v>100</v>
       </c>
-      <c r="I14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K14" t="s">
-        <v>33</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14">
+      <c r="I14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="0">
+        <v>0</v>
+      </c>
+      <c r="M14" s="0">
+        <v>0</v>
+      </c>
+      <c r="N14" s="0">
+        <v>1</v>
+      </c>
+      <c r="O14" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15">
+      <c r="A15" s="0">
         <v>1014</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="0">
         <v>150</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="0">
         <v>2</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="0">
         <v>35</v>
       </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="H15">
+      <c r="F15" s="0">
+        <v>1</v>
+      </c>
+      <c r="H15" s="0">
         <v>110</v>
       </c>
-      <c r="I15" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" t="s">
-        <v>33</v>
-      </c>
-      <c r="K15" t="s">
-        <v>33</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-      <c r="O15">
+      <c r="I15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="0">
+        <v>0</v>
+      </c>
+      <c r="M15" s="0">
+        <v>0</v>
+      </c>
+      <c r="N15" s="0">
+        <v>1</v>
+      </c>
+      <c r="O15" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16">
+      <c r="A16" s="0">
         <v>1015</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="0">
         <v>200</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="0">
         <v>3</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="0">
         <v>40</v>
       </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="H16">
+      <c r="F16" s="0">
+        <v>1</v>
+      </c>
+      <c r="H16" s="0">
         <v>120</v>
       </c>
-      <c r="I16" t="s">
-        <v>33</v>
-      </c>
-      <c r="J16" t="s">
-        <v>33</v>
-      </c>
-      <c r="K16" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-      <c r="O16">
+      <c r="I16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="0">
+        <v>0</v>
+      </c>
+      <c r="M16" s="0">
+        <v>0</v>
+      </c>
+      <c r="N16" s="0">
+        <v>1</v>
+      </c>
+      <c r="O16" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17">
+      <c r="A17" s="0">
         <v>1016</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="0">
         <v>150</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
+      <c r="D17" s="0">
+        <v>1</v>
+      </c>
+      <c r="E17" s="0">
         <v>50</v>
       </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17">
+      <c r="F17" s="0">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0">
         <v>120</v>
       </c>
-      <c r="I17" t="s">
-        <v>33</v>
-      </c>
-      <c r="J17" t="s">
-        <v>33</v>
-      </c>
-      <c r="K17" t="s">
-        <v>33</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17">
+      <c r="I17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="0">
+        <v>0</v>
+      </c>
+      <c r="M17" s="0">
+        <v>0</v>
+      </c>
+      <c r="N17" s="0">
+        <v>1</v>
+      </c>
+      <c r="O17" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18">
+      <c r="A18" s="0">
         <v>1017</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="0">
         <v>200</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="0">
         <v>2</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="0">
         <v>55</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="H18">
+      <c r="F18" s="0">
+        <v>1</v>
+      </c>
+      <c r="H18" s="0">
         <v>130</v>
       </c>
-      <c r="I18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J18" t="s">
-        <v>33</v>
-      </c>
-      <c r="K18" t="s">
-        <v>33</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
-      <c r="O18">
+      <c r="I18" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="0">
+        <v>0</v>
+      </c>
+      <c r="M18" s="0">
+        <v>0</v>
+      </c>
+      <c r="N18" s="0">
+        <v>1</v>
+      </c>
+      <c r="O18" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19">
+      <c r="A19" s="0">
         <v>1018</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="0">
         <v>250</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="0">
         <v>3</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="0">
         <v>60</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="H19">
+      <c r="F19" s="0">
+        <v>1</v>
+      </c>
+      <c r="H19" s="0">
         <v>140</v>
       </c>
-      <c r="I19" t="s">
-        <v>33</v>
-      </c>
-      <c r="J19" t="s">
-        <v>33</v>
-      </c>
-      <c r="K19" t="s">
-        <v>33</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19">
+      <c r="I19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" s="0">
+        <v>0</v>
+      </c>
+      <c r="M19" s="0">
+        <v>0</v>
+      </c>
+      <c r="N19" s="0">
+        <v>1</v>
+      </c>
+      <c r="O19" s="0">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>key</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>3_dark_spirit</t>
+  </si>
+  <si>
+    <t>TowerTier</t>
   </si>
 </sst>
 </file>
@@ -121,7 +124,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="19">
     <font>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
@@ -216,13 +219,6 @@
       <color rgb="FFFA7D00"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="1"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
@@ -245,12 +241,6 @@
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
       <color theme="0"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
       <i/>
@@ -491,7 +481,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -500,7 +489,6 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -509,7 +497,6 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -518,7 +505,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -533,7 +519,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -548,7 +533,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -563,7 +547,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -572,7 +555,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -583,7 +565,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
@@ -647,91 +628,91 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1080,10 +1061,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
+  <cols>
+    <col min="2" max="2" width="16.62999916" customWidth="1" outlineLevel="0"/>
+    <col min="8" max="8" width="11.75500011" customWidth="1" outlineLevel="0"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1129,8 +1114,11 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="0" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" s="0">
         <v>1001</v>
       </c>
@@ -1173,8 +1161,11 @@
       <c r="O2" s="0">
         <v>0</v>
       </c>
+      <c r="P2" s="0">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3" s="0">
         <v>1002</v>
       </c>
@@ -1217,8 +1208,11 @@
       <c r="O3" s="0">
         <v>0</v>
       </c>
+      <c r="P3" s="0">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="A4" s="0">
         <v>1003</v>
       </c>
@@ -1261,8 +1255,11 @@
       <c r="O4" s="0">
         <v>0</v>
       </c>
+      <c r="P4" s="0">
+        <v>3</v>
+      </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5" s="0">
         <v>1004</v>
       </c>
@@ -1305,8 +1302,11 @@
       <c r="O5" s="0">
         <v>0</v>
       </c>
+      <c r="P5" s="0">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6" s="0">
         <v>1005</v>
       </c>
@@ -1349,8 +1349,11 @@
       <c r="O6" s="0">
         <v>0</v>
       </c>
+      <c r="P6" s="0">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="A7" s="0">
         <v>1006</v>
       </c>
@@ -1393,8 +1396,11 @@
       <c r="O7" s="0">
         <v>0</v>
       </c>
+      <c r="P7" s="0">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="A8" s="0">
         <v>1007</v>
       </c>
@@ -1437,8 +1443,11 @@
       <c r="O8" s="0">
         <v>0</v>
       </c>
+      <c r="P8" s="0">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="A9" s="0">
         <v>1008</v>
       </c>
@@ -1481,8 +1490,11 @@
       <c r="O9" s="0">
         <v>0</v>
       </c>
+      <c r="P9" s="0">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10" s="0">
         <v>1009</v>
       </c>
@@ -1525,8 +1537,11 @@
       <c r="O10" s="0">
         <v>0</v>
       </c>
+      <c r="P10" s="0">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="A11" s="0">
         <v>1010</v>
       </c>
@@ -1569,8 +1584,11 @@
       <c r="O11" s="0">
         <v>0</v>
       </c>
+      <c r="P11" s="0">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="A12" s="0">
         <v>1011</v>
       </c>
@@ -1613,8 +1631,11 @@
       <c r="O12" s="0">
         <v>0</v>
       </c>
+      <c r="P12" s="0">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="A13" s="0">
         <v>1012</v>
       </c>
@@ -1657,8 +1678,11 @@
       <c r="O13" s="0">
         <v>0</v>
       </c>
+      <c r="P13" s="0">
+        <v>3</v>
+      </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="A14" s="0">
         <v>1013</v>
       </c>
@@ -1701,8 +1725,11 @@
       <c r="O14" s="0">
         <v>0</v>
       </c>
+      <c r="P14" s="0">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:16">
       <c r="A15" s="0">
         <v>1014</v>
       </c>
@@ -1745,8 +1772,11 @@
       <c r="O15" s="0">
         <v>0</v>
       </c>
+      <c r="P15" s="0">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:16">
       <c r="A16" s="0">
         <v>1015</v>
       </c>
@@ -1789,8 +1819,11 @@
       <c r="O16" s="0">
         <v>0</v>
       </c>
+      <c r="P16" s="0">
+        <v>3</v>
+      </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:16">
       <c r="A17" s="0">
         <v>1016</v>
       </c>
@@ -1833,8 +1866,11 @@
       <c r="O17" s="0">
         <v>0</v>
       </c>
+      <c r="P17" s="0">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:16">
       <c r="A18" s="0">
         <v>1017</v>
       </c>
@@ -1877,8 +1913,11 @@
       <c r="O18" s="0">
         <v>0</v>
       </c>
+      <c r="P18" s="0">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:16">
       <c r="A19" s="0">
         <v>1018</v>
       </c>
@@ -1920,6 +1959,9 @@
       </c>
       <c r="O19" s="0">
         <v>0</v>
+      </c>
+      <c r="P19" s="0">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>key</t>
   </si>
@@ -114,9 +114,6 @@
   </si>
   <si>
     <t>3_dark_spirit</t>
-  </si>
-  <si>
-    <t>TowerTier</t>
   </si>
 </sst>
 </file>
@@ -1061,14 +1058,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
-  <cols>
-    <col min="2" max="2" width="16.62999916" customWidth="1" outlineLevel="0"/>
-    <col min="8" max="8" width="11.75500011" customWidth="1" outlineLevel="0"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1114,11 +1107,8 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="0" t="s">
-        <v>33</v>
-      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:15">
       <c r="A2" s="0">
         <v>1001</v>
       </c>
@@ -1161,11 +1151,8 @@
       <c r="O2" s="0">
         <v>0</v>
       </c>
-      <c r="P2" s="0">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:15">
       <c r="A3" s="0">
         <v>1002</v>
       </c>
@@ -1208,11 +1195,8 @@
       <c r="O3" s="0">
         <v>0</v>
       </c>
-      <c r="P3" s="0">
-        <v>2</v>
-      </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:15">
       <c r="A4" s="0">
         <v>1003</v>
       </c>
@@ -1255,11 +1239,8 @@
       <c r="O4" s="0">
         <v>0</v>
       </c>
-      <c r="P4" s="0">
-        <v>3</v>
-      </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:15">
       <c r="A5" s="0">
         <v>1004</v>
       </c>
@@ -1282,7 +1263,7 @@
         <v>30</v>
       </c>
       <c r="I5" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="0" t="b">
         <v>0</v>
@@ -1291,10 +1272,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="0">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M5" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5" s="0">
         <v>1</v>
@@ -1302,11 +1283,8 @@
       <c r="O5" s="0">
         <v>0</v>
       </c>
-      <c r="P5" s="0">
-        <v>1</v>
-      </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:15">
       <c r="A6" s="0">
         <v>1005</v>
       </c>
@@ -1329,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="I6" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="0" t="b">
         <v>0</v>
@@ -1338,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="0">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M6" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" s="0">
         <v>1</v>
@@ -1349,11 +1327,8 @@
       <c r="O6" s="0">
         <v>0</v>
       </c>
-      <c r="P6" s="0">
-        <v>2</v>
-      </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:15">
       <c r="A7" s="0">
         <v>1006</v>
       </c>
@@ -1376,7 +1351,7 @@
         <v>50</v>
       </c>
       <c r="I7" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="0" t="b">
         <v>0</v>
@@ -1385,10 +1360,10 @@
         <v>0</v>
       </c>
       <c r="L7" s="0">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M7" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N7" s="0">
         <v>1</v>
@@ -1396,11 +1371,8 @@
       <c r="O7" s="0">
         <v>0</v>
       </c>
-      <c r="P7" s="0">
-        <v>3</v>
-      </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:15">
       <c r="A8" s="0">
         <v>1007</v>
       </c>
@@ -1426,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -1438,16 +1410,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O8" s="0">
         <v>0</v>
       </c>
-      <c r="P8" s="0">
-        <v>1</v>
-      </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:15">
       <c r="A9" s="0">
         <v>1008</v>
       </c>
@@ -1473,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>0</v>
@@ -1485,16 +1454,13 @@
         <v>0</v>
       </c>
       <c r="N9" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O9" s="0">
         <v>0</v>
       </c>
-      <c r="P9" s="0">
-        <v>2</v>
-      </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:15">
       <c r="A10" s="0">
         <v>1009</v>
       </c>
@@ -1520,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -1532,16 +1498,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O10" s="0">
         <v>0</v>
       </c>
-      <c r="P10" s="0">
-        <v>3</v>
-      </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:15">
       <c r="A11" s="0">
         <v>1010</v>
       </c>
@@ -1584,11 +1547,8 @@
       <c r="O11" s="0">
         <v>0</v>
       </c>
-      <c r="P11" s="0">
-        <v>1</v>
-      </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:15">
       <c r="A12" s="0">
         <v>1011</v>
       </c>
@@ -1631,11 +1591,8 @@
       <c r="O12" s="0">
         <v>0</v>
       </c>
-      <c r="P12" s="0">
-        <v>2</v>
-      </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:15">
       <c r="A13" s="0">
         <v>1012</v>
       </c>
@@ -1678,11 +1635,8 @@
       <c r="O13" s="0">
         <v>0</v>
       </c>
-      <c r="P13" s="0">
-        <v>3</v>
-      </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:15">
       <c r="A14" s="0">
         <v>1013</v>
       </c>
@@ -1711,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="0">
         <v>0</v>
@@ -1723,13 +1677,10 @@
         <v>1</v>
       </c>
       <c r="O14" s="0">
-        <v>0</v>
-      </c>
-      <c r="P14" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:15">
       <c r="A15" s="0">
         <v>1014</v>
       </c>
@@ -1758,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="0">
         <v>0</v>
@@ -1770,13 +1721,10 @@
         <v>1</v>
       </c>
       <c r="O15" s="0">
-        <v>0</v>
-      </c>
-      <c r="P15" s="0">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:15">
       <c r="A16" s="0">
         <v>1015</v>
       </c>
@@ -1805,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="0">
         <v>0</v>
@@ -1817,13 +1765,10 @@
         <v>1</v>
       </c>
       <c r="O16" s="0">
-        <v>0</v>
-      </c>
-      <c r="P16" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:15">
       <c r="A17" s="0">
         <v>1016</v>
       </c>
@@ -1866,11 +1811,8 @@
       <c r="O17" s="0">
         <v>0</v>
       </c>
-      <c r="P17" s="0">
-        <v>1</v>
-      </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:15">
       <c r="A18" s="0">
         <v>1017</v>
       </c>
@@ -1913,11 +1855,8 @@
       <c r="O18" s="0">
         <v>0</v>
       </c>
-      <c r="P18" s="0">
-        <v>2</v>
-      </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:15">
       <c r="A19" s="0">
         <v>1018</v>
       </c>
@@ -1959,9 +1898,6 @@
       </c>
       <c r="O19" s="0">
         <v>0</v>
-      </c>
-      <c r="P19" s="0">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>key</t>
   </si>
@@ -114,6 +114,21 @@
   </si>
   <si>
     <t>3_dark_spirit</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>flaot</t>
+  </si>
+  <si>
+    <t>bool</t>
   </si>
 </sst>
 </file>
@@ -121,7 +136,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="19">
     <font>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
@@ -216,13 +231,6 @@
       <color rgb="FFFA7D00"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="1"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
@@ -247,12 +255,6 @@
       <color theme="0"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="1"/>
-    </font>
-    <font>
       <i/>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
@@ -457,7 +459,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -491,7 +493,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -500,7 +501,6 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -509,7 +509,6 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -518,7 +517,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -533,7 +531,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -548,7 +545,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -563,7 +559,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -572,7 +567,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -583,7 +577,12 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="49">
@@ -647,97 +646,100 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1080,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -1131,70 +1133,73 @@
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="0">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="0">
-        <v>50</v>
-      </c>
-      <c r="D2" s="0">
-        <v>1</v>
-      </c>
-      <c r="E2" s="0">
-        <v>5</v>
-      </c>
-      <c r="F2" s="0">
-        <v>1</v>
-      </c>
-      <c r="G2" s="0">
-        <v>20</v>
-      </c>
-      <c r="I2" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" s="0">
-        <v>0</v>
-      </c>
-      <c r="M2" s="0">
-        <v>0</v>
-      </c>
-      <c r="N2" s="0">
-        <v>1</v>
-      </c>
-      <c r="O2" s="0">
-        <v>0</v>
+      <c r="A2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="0">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="0">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D3" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3" s="0">
         <v>1</v>
       </c>
-      <c r="H3" s="0">
-        <v>30</v>
+      <c r="G3" s="0">
+        <v>20</v>
       </c>
       <c r="I3" s="0" t="b">
         <v>0</v>
@@ -1220,25 +1225,25 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="0">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="0">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D4" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" s="0">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F4" s="0">
         <v>1</v>
       </c>
       <c r="H4" s="0">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I4" s="0" t="b">
         <v>0</v>
@@ -1264,25 +1269,25 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="0">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="0">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D5" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" s="0">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F5" s="0">
         <v>1</v>
       </c>
-      <c r="G5" s="0">
-        <v>30</v>
+      <c r="H5" s="0">
+        <v>40</v>
       </c>
       <c r="I5" s="0" t="b">
         <v>0</v>
@@ -1308,25 +1313,25 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="0">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="0">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D6" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" s="0">
         <v>1</v>
       </c>
-      <c r="H6" s="0">
-        <v>40</v>
+      <c r="G6" s="0">
+        <v>30</v>
       </c>
       <c r="I6" s="0" t="b">
         <v>0</v>
@@ -1352,25 +1357,25 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="0">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="0">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D7" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="0">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F7" s="0">
         <v>1</v>
       </c>
       <c r="H7" s="0">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I7" s="0" t="b">
         <v>0</v>
@@ -1396,24 +1401,24 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="0">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="0">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D8" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="0">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F8" s="0">
         <v>1</v>
       </c>
-      <c r="G8" s="0">
+      <c r="H8" s="0">
         <v>50</v>
       </c>
       <c r="I8" s="0" t="b">
@@ -1440,25 +1445,25 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="0">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="0">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D9" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" s="0">
         <v>1</v>
       </c>
-      <c r="H9" s="0">
-        <v>60</v>
+      <c r="G9" s="0">
+        <v>50</v>
       </c>
       <c r="I9" s="0" t="b">
         <v>0</v>
@@ -1484,25 +1489,25 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="0">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="0">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D10" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="0">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F10" s="0">
         <v>1</v>
       </c>
       <c r="H10" s="0">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I10" s="0" t="b">
         <v>0</v>
@@ -1528,25 +1533,25 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="0">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="0">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="D11" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" s="0">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F11" s="0">
-        <v>0</v>
-      </c>
-      <c r="G11" s="0">
-        <v>75</v>
+        <v>1</v>
+      </c>
+      <c r="H11" s="0">
+        <v>70</v>
       </c>
       <c r="I11" s="0" t="b">
         <v>0</v>
@@ -1572,16 +1577,16 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="0">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="0">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="D12" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="0">
         <v>0</v>
@@ -1589,8 +1594,8 @@
       <c r="F12" s="0">
         <v>0</v>
       </c>
-      <c r="H12" s="0">
-        <v>80</v>
+      <c r="G12" s="0">
+        <v>75</v>
       </c>
       <c r="I12" s="0" t="b">
         <v>0</v>
@@ -1616,16 +1621,16 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="0">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="0">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="D13" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="0">
         <v>0</v>
@@ -1634,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="0">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I13" s="0" t="b">
         <v>0</v>
@@ -1660,25 +1665,25 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="0">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="0">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="D14" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="0">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F14" s="0">
-        <v>1</v>
-      </c>
-      <c r="G14" s="0">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="H14" s="0">
+        <v>95</v>
       </c>
       <c r="I14" s="0" t="b">
         <v>0</v>
@@ -1704,25 +1709,25 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="0">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="0">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D15" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="0">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F15" s="0">
         <v>1</v>
       </c>
-      <c r="H15" s="0">
-        <v>110</v>
+      <c r="G15" s="0">
+        <v>100</v>
       </c>
       <c r="I15" s="0" t="b">
         <v>0</v>
@@ -1748,25 +1753,25 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="0">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="0">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D16" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="0">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F16" s="0">
         <v>1</v>
       </c>
       <c r="H16" s="0">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I16" s="0" t="b">
         <v>0</v>
@@ -1792,24 +1797,24 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="0">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="0">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="D17" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="0">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F17" s="0">
         <v>1</v>
       </c>
-      <c r="G17" s="0">
+      <c r="H17" s="0">
         <v>120</v>
       </c>
       <c r="I17" s="0" t="b">
@@ -1836,25 +1841,25 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="0">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="0">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D18" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="0">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F18" s="0">
         <v>1</v>
       </c>
-      <c r="H18" s="0">
-        <v>130</v>
+      <c r="G18" s="0">
+        <v>120</v>
       </c>
       <c r="I18" s="0" t="b">
         <v>0</v>
@@ -1880,45 +1885,89 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="0">
+        <v>1017</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="0">
+        <v>200</v>
+      </c>
+      <c r="D19" s="0">
+        <v>2</v>
+      </c>
+      <c r="E19" s="0">
+        <v>55</v>
+      </c>
+      <c r="F19" s="0">
+        <v>1</v>
+      </c>
+      <c r="H19" s="0">
+        <v>130</v>
+      </c>
+      <c r="I19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" s="0">
+        <v>0</v>
+      </c>
+      <c r="M19" s="0">
+        <v>0</v>
+      </c>
+      <c r="N19" s="0">
+        <v>1</v>
+      </c>
+      <c r="O19" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="0">
         <v>1018</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B20" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="0">
+      <c r="C20" s="0">
         <v>250</v>
       </c>
-      <c r="D19" s="0">
+      <c r="D20" s="0">
         <v>3</v>
       </c>
-      <c r="E19" s="0">
+      <c r="E20" s="0">
         <v>60</v>
       </c>
-      <c r="F19" s="0">
-        <v>1</v>
-      </c>
-      <c r="H19" s="0">
+      <c r="F20" s="0">
+        <v>1</v>
+      </c>
+      <c r="H20" s="0">
         <v>140</v>
       </c>
-      <c r="I19" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" s="0">
-        <v>0</v>
-      </c>
-      <c r="M19" s="0">
-        <v>0</v>
-      </c>
-      <c r="N19" s="0">
-        <v>1</v>
-      </c>
-      <c r="O19" s="0">
+      <c r="I20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="0">
+        <v>0</v>
+      </c>
+      <c r="M20" s="0">
+        <v>0</v>
+      </c>
+      <c r="N20" s="0">
+        <v>1</v>
+      </c>
+      <c r="O20" s="0">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>key</t>
   </si>
@@ -114,21 +114,6 @@
   </si>
   <si>
     <t>3_dark_spirit</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>flaot</t>
-  </si>
-  <si>
-    <t>bool</t>
   </si>
 </sst>
 </file>
@@ -136,7 +121,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
@@ -231,9 +216,16 @@
       <color rgb="FFFA7D00"/>
     </font>
     <font>
+      <b/>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color rgb="FF006100"/>
     </font>
     <font>
@@ -253,6 +245,12 @@
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
       <color theme="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="1"/>
     </font>
     <font>
       <i/>
@@ -459,7 +457,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -493,6 +491,7 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -501,6 +500,7 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -509,6 +509,7 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -517,6 +518,7 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -531,6 +533,7 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -545,6 +548,7 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -559,6 +563,7 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -567,6 +572,7 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -577,12 +583,7 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
@@ -646,100 +647,97 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1082,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -1133,73 +1131,70 @@
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>35</v>
+      <c r="A2" s="0">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="0">
+        <v>50</v>
+      </c>
+      <c r="D2" s="0">
+        <v>1</v>
+      </c>
+      <c r="E2" s="0">
+        <v>5</v>
+      </c>
+      <c r="F2" s="0">
+        <v>1</v>
+      </c>
+      <c r="G2" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" s="0">
+        <v>0</v>
+      </c>
+      <c r="M2" s="0">
+        <v>0</v>
+      </c>
+      <c r="N2" s="0">
+        <v>1</v>
+      </c>
+      <c r="O2" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="0">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="0">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D3" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="0">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F3" s="0">
         <v>1</v>
       </c>
-      <c r="G3" s="0">
-        <v>20</v>
+      <c r="H3" s="0">
+        <v>30</v>
       </c>
       <c r="I3" s="0" t="b">
         <v>0</v>
@@ -1225,25 +1220,25 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="0">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="0">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D4" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="0">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F4" s="0">
         <v>1</v>
       </c>
       <c r="H4" s="0">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I4" s="0" t="b">
         <v>0</v>
@@ -1269,25 +1264,25 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="0">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="0">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D5" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" s="0">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F5" s="0">
         <v>1</v>
       </c>
-      <c r="H5" s="0">
-        <v>40</v>
+      <c r="G5" s="0">
+        <v>30</v>
       </c>
       <c r="I5" s="0" t="b">
         <v>0</v>
@@ -1313,25 +1308,25 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="0">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="0">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D6" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="0">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" s="0">
         <v>1</v>
       </c>
-      <c r="G6" s="0">
-        <v>30</v>
+      <c r="H6" s="0">
+        <v>40</v>
       </c>
       <c r="I6" s="0" t="b">
         <v>0</v>
@@ -1357,25 +1352,25 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="0">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="0">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D7" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="0">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F7" s="0">
         <v>1</v>
       </c>
       <c r="H7" s="0">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I7" s="0" t="b">
         <v>0</v>
@@ -1401,24 +1396,24 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="0">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="0">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D8" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" s="0">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F8" s="0">
         <v>1</v>
       </c>
-      <c r="H8" s="0">
+      <c r="G8" s="0">
         <v>50</v>
       </c>
       <c r="I8" s="0" t="b">
@@ -1445,25 +1440,25 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="0">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="0">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D9" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="0">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" s="0">
         <v>1</v>
       </c>
-      <c r="G9" s="0">
-        <v>50</v>
+      <c r="H9" s="0">
+        <v>60</v>
       </c>
       <c r="I9" s="0" t="b">
         <v>0</v>
@@ -1489,25 +1484,25 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="0">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="0">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D10" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="0">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F10" s="0">
         <v>1</v>
       </c>
       <c r="H10" s="0">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I10" s="0" t="b">
         <v>0</v>
@@ -1533,25 +1528,25 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="0">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="0">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="D11" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" s="0">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F11" s="0">
-        <v>1</v>
-      </c>
-      <c r="H11" s="0">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="G11" s="0">
+        <v>75</v>
       </c>
       <c r="I11" s="0" t="b">
         <v>0</v>
@@ -1577,16 +1572,16 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="0">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="0">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="D12" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="0">
         <v>0</v>
@@ -1594,8 +1589,8 @@
       <c r="F12" s="0">
         <v>0</v>
       </c>
-      <c r="G12" s="0">
-        <v>75</v>
+      <c r="H12" s="0">
+        <v>80</v>
       </c>
       <c r="I12" s="0" t="b">
         <v>0</v>
@@ -1621,16 +1616,16 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="0">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" s="0">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="D13" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="0">
         <v>0</v>
@@ -1639,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="0">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I13" s="0" t="b">
         <v>0</v>
@@ -1665,25 +1660,25 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="0">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" s="0">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="D14" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" s="0">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F14" s="0">
-        <v>0</v>
-      </c>
-      <c r="H14" s="0">
-        <v>95</v>
+        <v>1</v>
+      </c>
+      <c r="G14" s="0">
+        <v>100</v>
       </c>
       <c r="I14" s="0" t="b">
         <v>0</v>
@@ -1709,25 +1704,25 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="0">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="0">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D15" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="0">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F15" s="0">
         <v>1</v>
       </c>
-      <c r="G15" s="0">
-        <v>100</v>
+      <c r="H15" s="0">
+        <v>110</v>
       </c>
       <c r="I15" s="0" t="b">
         <v>0</v>
@@ -1753,25 +1748,25 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="0">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" s="0">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="D16" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="0">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F16" s="0">
         <v>1</v>
       </c>
       <c r="H16" s="0">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="I16" s="0" t="b">
         <v>0</v>
@@ -1797,24 +1792,24 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="0">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" s="0">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D17" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="0">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F17" s="0">
         <v>1</v>
       </c>
-      <c r="H17" s="0">
+      <c r="G17" s="0">
         <v>120</v>
       </c>
       <c r="I17" s="0" t="b">
@@ -1841,25 +1836,25 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="0">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" s="0">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="D18" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="0">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F18" s="0">
         <v>1</v>
       </c>
-      <c r="G18" s="0">
-        <v>120</v>
+      <c r="H18" s="0">
+        <v>130</v>
       </c>
       <c r="I18" s="0" t="b">
         <v>0</v>
@@ -1885,25 +1880,25 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="0">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C19" s="0">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D19" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="0">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F19" s="0">
         <v>1</v>
       </c>
       <c r="H19" s="0">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I19" s="0" t="b">
         <v>0</v>
@@ -1924,50 +1919,6 @@
         <v>1</v>
       </c>
       <c r="O19" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="0">
-        <v>1018</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="0">
-        <v>250</v>
-      </c>
-      <c r="D20" s="0">
-        <v>3</v>
-      </c>
-      <c r="E20" s="0">
-        <v>60</v>
-      </c>
-      <c r="F20" s="0">
-        <v>1</v>
-      </c>
-      <c r="H20" s="0">
-        <v>140</v>
-      </c>
-      <c r="I20" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" s="0">
-        <v>0</v>
-      </c>
-      <c r="M20" s="0">
-        <v>0</v>
-      </c>
-      <c r="N20" s="0">
-        <v>1</v>
-      </c>
-      <c r="O20" s="0">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>key</t>
   </si>
@@ -129,6 +129,36 @@
   </si>
   <si>
     <t>bool</t>
+  </si>
+  <si>
+    <t>TURE</t>
+  </si>
+  <si>
+    <t>ToweType</t>
+  </si>
+  <si>
+    <t>enum</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>slow</t>
+  </si>
+  <si>
+    <t>Slow</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>Pierce</t>
+  </si>
+  <si>
+    <t>Stun</t>
+  </si>
+  <si>
+    <t>TowerType</t>
   </si>
 </sst>
 </file>
@@ -459,7 +489,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -578,12 +608,6 @@
         <color theme="4"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -739,7 +763,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1082,10 +1106,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
+  <cols>
+    <col min="9" max="9" width="9.00500011" customWidth="1" outlineLevel="0"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1111,28 +1138,22 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
@@ -1158,28 +1179,22 @@
         <v>33</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:13">
       <c r="A3" s="0">
         <v>1001</v>
       </c>
@@ -1201,29 +1216,26 @@
       <c r="G3" s="0">
         <v>20</v>
       </c>
-      <c r="I3" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" s="0" t="b">
+      <c r="H3" s="0">
+        <v>0</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="0">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0">
         <v>0</v>
       </c>
       <c r="L3" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="0">
         <v>0</v>
       </c>
-      <c r="N3" s="0">
-        <v>1</v>
-      </c>
-      <c r="O3" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:13">
       <c r="A4" s="0">
         <v>1002</v>
       </c>
@@ -1242,32 +1254,29 @@
       <c r="F4" s="0">
         <v>1</v>
       </c>
+      <c r="G4" s="0">
+        <v>0</v>
+      </c>
       <c r="H4" s="0">
         <v>30</v>
       </c>
-      <c r="I4" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="0" t="b">
+      <c r="I4" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="0">
+        <v>0</v>
+      </c>
+      <c r="K4" s="0">
         <v>0</v>
       </c>
       <c r="L4" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="0">
         <v>0</v>
       </c>
-      <c r="N4" s="0">
-        <v>1</v>
-      </c>
-      <c r="O4" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:13">
       <c r="A5" s="0">
         <v>1003</v>
       </c>
@@ -1286,32 +1295,29 @@
       <c r="F5" s="0">
         <v>1</v>
       </c>
+      <c r="G5" s="0">
+        <v>0</v>
+      </c>
       <c r="H5" s="0">
         <v>40</v>
       </c>
-      <c r="I5" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0" t="b">
+      <c r="I5" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="0">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0">
         <v>0</v>
       </c>
       <c r="L5" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="0">
         <v>0</v>
       </c>
-      <c r="N5" s="0">
-        <v>1</v>
-      </c>
-      <c r="O5" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:13">
       <c r="A6" s="0">
         <v>1004</v>
       </c>
@@ -1333,29 +1339,26 @@
       <c r="G6" s="0">
         <v>30</v>
       </c>
-      <c r="I6" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0" t="b">
+      <c r="H6" s="0">
+        <v>0</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="0">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0">
         <v>0</v>
       </c>
       <c r="L6" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="0">
         <v>0</v>
       </c>
-      <c r="N6" s="0">
-        <v>1</v>
-      </c>
-      <c r="O6" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:13">
       <c r="A7" s="0">
         <v>1005</v>
       </c>
@@ -1374,32 +1377,29 @@
       <c r="F7" s="0">
         <v>1</v>
       </c>
+      <c r="G7" s="0">
+        <v>0</v>
+      </c>
       <c r="H7" s="0">
         <v>40</v>
       </c>
-      <c r="I7" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="0" t="b">
+      <c r="I7" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="0">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0">
         <v>0</v>
       </c>
       <c r="L7" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="0">
         <v>0</v>
       </c>
-      <c r="N7" s="0">
-        <v>1</v>
-      </c>
-      <c r="O7" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:13">
       <c r="A8" s="0">
         <v>1006</v>
       </c>
@@ -1418,32 +1418,29 @@
       <c r="F8" s="0">
         <v>1</v>
       </c>
+      <c r="G8" s="0">
+        <v>0</v>
+      </c>
       <c r="H8" s="0">
         <v>50</v>
       </c>
-      <c r="I8" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0" t="b">
+      <c r="I8" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="0">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0">
         <v>0</v>
       </c>
       <c r="L8" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="0">
         <v>0</v>
       </c>
-      <c r="N8" s="0">
-        <v>1</v>
-      </c>
-      <c r="O8" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:13">
       <c r="A9" s="0">
         <v>1007</v>
       </c>
@@ -1465,29 +1462,26 @@
       <c r="G9" s="0">
         <v>50</v>
       </c>
-      <c r="I9" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0" t="b">
+      <c r="H9" s="0">
+        <v>0</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" s="0">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0">
         <v>0</v>
       </c>
       <c r="L9" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="0">
         <v>0</v>
       </c>
-      <c r="N9" s="0">
-        <v>1</v>
-      </c>
-      <c r="O9" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:13">
       <c r="A10" s="0">
         <v>1008</v>
       </c>
@@ -1506,32 +1500,29 @@
       <c r="F10" s="0">
         <v>1</v>
       </c>
+      <c r="G10" s="0">
+        <v>0</v>
+      </c>
       <c r="H10" s="0">
         <v>60</v>
       </c>
-      <c r="I10" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0" t="b">
+      <c r="I10" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="0">
+        <v>0</v>
+      </c>
+      <c r="K10" s="0">
         <v>0</v>
       </c>
       <c r="L10" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="0">
         <v>0</v>
       </c>
-      <c r="N10" s="0">
-        <v>1</v>
-      </c>
-      <c r="O10" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:13">
       <c r="A11" s="0">
         <v>1009</v>
       </c>
@@ -1550,32 +1541,29 @@
       <c r="F11" s="0">
         <v>1</v>
       </c>
+      <c r="G11" s="0">
+        <v>0</v>
+      </c>
       <c r="H11" s="0">
         <v>70</v>
       </c>
-      <c r="I11" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0" t="b">
+      <c r="I11" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" s="0">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0">
         <v>0</v>
       </c>
       <c r="L11" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="0">
         <v>0</v>
       </c>
-      <c r="N11" s="0">
-        <v>1</v>
-      </c>
-      <c r="O11" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:13">
       <c r="A12" s="0">
         <v>1010</v>
       </c>
@@ -1597,29 +1585,26 @@
       <c r="G12" s="0">
         <v>75</v>
       </c>
-      <c r="I12" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="0" t="b">
+      <c r="H12" s="0">
+        <v>0</v>
+      </c>
+      <c r="I12" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="0">
+        <v>0</v>
+      </c>
+      <c r="K12" s="0">
         <v>0</v>
       </c>
       <c r="L12" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="0">
         <v>0</v>
       </c>
-      <c r="N12" s="0">
-        <v>1</v>
-      </c>
-      <c r="O12" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:13">
       <c r="A13" s="0">
         <v>1011</v>
       </c>
@@ -1638,32 +1623,29 @@
       <c r="F13" s="0">
         <v>0</v>
       </c>
+      <c r="G13" s="0">
+        <v>0</v>
+      </c>
       <c r="H13" s="0">
         <v>80</v>
       </c>
-      <c r="I13" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" s="0" t="b">
+      <c r="I13" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="0">
+        <v>0</v>
+      </c>
+      <c r="K13" s="0">
         <v>0</v>
       </c>
       <c r="L13" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="0">
         <v>0</v>
       </c>
-      <c r="N13" s="0">
-        <v>1</v>
-      </c>
-      <c r="O13" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:13">
       <c r="A14" s="0">
         <v>1012</v>
       </c>
@@ -1682,32 +1664,29 @@
       <c r="F14" s="0">
         <v>0</v>
       </c>
+      <c r="G14" s="0">
+        <v>0</v>
+      </c>
       <c r="H14" s="0">
         <v>95</v>
       </c>
-      <c r="I14" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="0" t="b">
+      <c r="I14" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="0">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0">
         <v>0</v>
       </c>
       <c r="L14" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="0">
         <v>0</v>
       </c>
-      <c r="N14" s="0">
-        <v>1</v>
-      </c>
-      <c r="O14" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:13">
       <c r="A15" s="0">
         <v>1013</v>
       </c>
@@ -1729,29 +1708,26 @@
       <c r="G15" s="0">
         <v>100</v>
       </c>
-      <c r="I15" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" s="0" t="b">
+      <c r="H15" s="0">
+        <v>0</v>
+      </c>
+      <c r="I15" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="0">
+        <v>0</v>
+      </c>
+      <c r="K15" s="0">
         <v>0</v>
       </c>
       <c r="L15" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="0">
         <v>0</v>
       </c>
-      <c r="N15" s="0">
-        <v>1</v>
-      </c>
-      <c r="O15" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:13">
       <c r="A16" s="0">
         <v>1014</v>
       </c>
@@ -1770,32 +1746,29 @@
       <c r="F16" s="0">
         <v>1</v>
       </c>
+      <c r="G16" s="0">
+        <v>0</v>
+      </c>
       <c r="H16" s="0">
         <v>110</v>
       </c>
-      <c r="I16" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" s="0" t="b">
+      <c r="I16" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="0">
+        <v>0</v>
+      </c>
+      <c r="K16" s="0">
         <v>0</v>
       </c>
       <c r="L16" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="0">
         <v>0</v>
       </c>
-      <c r="N16" s="0">
-        <v>1</v>
-      </c>
-      <c r="O16" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:13">
       <c r="A17" s="0">
         <v>1015</v>
       </c>
@@ -1814,32 +1787,29 @@
       <c r="F17" s="0">
         <v>1</v>
       </c>
+      <c r="G17" s="0">
+        <v>0</v>
+      </c>
       <c r="H17" s="0">
         <v>120</v>
       </c>
-      <c r="I17" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" s="0" t="b">
+      <c r="I17" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="0">
+        <v>0</v>
+      </c>
+      <c r="K17" s="0">
         <v>0</v>
       </c>
       <c r="L17" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="0">
         <v>0</v>
       </c>
-      <c r="N17" s="0">
-        <v>1</v>
-      </c>
-      <c r="O17" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:13">
       <c r="A18" s="0">
         <v>1016</v>
       </c>
@@ -1861,29 +1831,26 @@
       <c r="G18" s="0">
         <v>120</v>
       </c>
-      <c r="I18" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" s="0" t="b">
+      <c r="H18" s="0">
+        <v>0</v>
+      </c>
+      <c r="I18" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="0">
+        <v>0</v>
+      </c>
+      <c r="K18" s="0">
         <v>0</v>
       </c>
       <c r="L18" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="0">
         <v>0</v>
       </c>
-      <c r="N18" s="0">
-        <v>1</v>
-      </c>
-      <c r="O18" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:13">
       <c r="A19" s="0">
         <v>1017</v>
       </c>
@@ -1902,32 +1869,29 @@
       <c r="F19" s="0">
         <v>1</v>
       </c>
+      <c r="G19" s="0">
+        <v>0</v>
+      </c>
       <c r="H19" s="0">
         <v>130</v>
       </c>
-      <c r="I19" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" s="0" t="b">
+      <c r="I19" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="0">
+        <v>0</v>
+      </c>
+      <c r="K19" s="0">
         <v>0</v>
       </c>
       <c r="L19" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="0">
         <v>0</v>
       </c>
-      <c r="N19" s="0">
-        <v>1</v>
-      </c>
-      <c r="O19" s="0">
-        <v>0</v>
-      </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:13">
       <c r="A20" s="0">
         <v>1018</v>
       </c>
@@ -1946,28 +1910,25 @@
       <c r="F20" s="0">
         <v>1</v>
       </c>
+      <c r="G20" s="0">
+        <v>0</v>
+      </c>
       <c r="H20" s="0">
         <v>140</v>
       </c>
-      <c r="I20" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" s="0" t="b">
+      <c r="I20" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="0">
+        <v>0</v>
+      </c>
+      <c r="K20" s="0">
         <v>0</v>
       </c>
       <c r="L20" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="0">
-        <v>0</v>
-      </c>
-      <c r="N20" s="0">
-        <v>1</v>
-      </c>
-      <c r="O20" s="0">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>key</t>
   </si>
@@ -159,13 +159,21 @@
   </si>
   <si>
     <t>TowerType</t>
+  </si>
+  <si>
+    <t>()0.0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="64" formatCode="0.0_ "/>
+    <numFmt numFmtId="65" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="66" formatCode="0.00_ "/>
+    <numFmt numFmtId="67" formatCode="0.000_);[Red]\(0.000\)"/>
+  </numFmts>
   <fonts count="19">
     <font>
       <sz val="11.0"/>
@@ -758,7 +766,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -766,6 +774,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="64" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="65" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="66" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="67" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
@@ -1109,6 +1121,7 @@
   <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
+    <col min="3" max="3" width="9.88000011" customWidth="1" outlineLevel="0"/>
     <col min="9" max="9" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
@@ -1161,7 +1174,7 @@
         <v>34</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
@@ -1201,16 +1214,16 @@
       <c r="B3" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C3" s="6">
         <v>50</v>
       </c>
       <c r="D3" s="0">
         <v>1</v>
       </c>
-      <c r="E3" s="0">
+      <c r="E3" s="6">
         <v>5</v>
       </c>
-      <c r="F3" s="0">
+      <c r="F3" s="6">
         <v>1</v>
       </c>
       <c r="G3" s="0">
@@ -1222,16 +1235,16 @@
       <c r="I3" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="0">
-        <v>0</v>
-      </c>
-      <c r="K3" s="0">
+      <c r="J3" s="6">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6">
         <v>0</v>
       </c>
       <c r="L3" s="0">
         <v>1</v>
       </c>
-      <c r="M3" s="0">
+      <c r="M3" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1242,16 +1255,16 @@
       <c r="B4" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="0">
+      <c r="C4" s="6">
         <v>100</v>
       </c>
       <c r="D4" s="0">
         <v>2</v>
       </c>
-      <c r="E4" s="0">
+      <c r="E4" s="6">
         <v>10</v>
       </c>
-      <c r="F4" s="0">
+      <c r="F4" s="6">
         <v>1</v>
       </c>
       <c r="G4" s="0">
@@ -1263,16 +1276,16 @@
       <c r="I4" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="0">
-        <v>0</v>
-      </c>
-      <c r="K4" s="0">
+      <c r="J4" s="6">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6">
         <v>0</v>
       </c>
       <c r="L4" s="0">
         <v>1</v>
       </c>
-      <c r="M4" s="0">
+      <c r="M4" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1283,16 +1296,16 @@
       <c r="B5" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="0">
+      <c r="C5" s="6">
         <v>150</v>
       </c>
       <c r="D5" s="0">
         <v>3</v>
       </c>
-      <c r="E5" s="0">
+      <c r="E5" s="6">
         <v>20</v>
       </c>
-      <c r="F5" s="0">
+      <c r="F5" s="6">
         <v>1</v>
       </c>
       <c r="G5" s="0">
@@ -1304,16 +1317,16 @@
       <c r="I5" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="J5" s="0">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0">
+      <c r="J5" s="6">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6">
         <v>0</v>
       </c>
       <c r="L5" s="0">
         <v>1</v>
       </c>
-      <c r="M5" s="0">
+      <c r="M5" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1324,16 +1337,16 @@
       <c r="B6" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6" s="6">
         <v>50</v>
       </c>
       <c r="D6" s="0">
         <v>1</v>
       </c>
-      <c r="E6" s="0">
+      <c r="E6" s="6">
         <v>5</v>
       </c>
-      <c r="F6" s="0">
+      <c r="F6" s="6">
         <v>1</v>
       </c>
       <c r="G6" s="0">
@@ -1345,16 +1358,16 @@
       <c r="I6" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="0">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0">
+      <c r="J6" s="6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6">
         <v>0</v>
       </c>
       <c r="L6" s="0">
         <v>1</v>
       </c>
-      <c r="M6" s="0">
+      <c r="M6" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1365,16 +1378,16 @@
       <c r="B7" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="0">
+      <c r="C7" s="6">
         <v>100</v>
       </c>
       <c r="D7" s="0">
         <v>2</v>
       </c>
-      <c r="E7" s="0">
+      <c r="E7" s="6">
         <v>10</v>
       </c>
-      <c r="F7" s="0">
+      <c r="F7" s="6">
         <v>1</v>
       </c>
       <c r="G7" s="0">
@@ -1386,16 +1399,16 @@
       <c r="I7" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="0">
-        <v>0</v>
-      </c>
-      <c r="K7" s="0">
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
         <v>0</v>
       </c>
       <c r="L7" s="0">
         <v>1</v>
       </c>
-      <c r="M7" s="0">
+      <c r="M7" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1406,16 +1419,16 @@
       <c r="B8" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="0">
+      <c r="C8" s="6">
         <v>150</v>
       </c>
       <c r="D8" s="0">
         <v>3</v>
       </c>
-      <c r="E8" s="0">
+      <c r="E8" s="6">
         <v>20</v>
       </c>
-      <c r="F8" s="0">
+      <c r="F8" s="6">
         <v>1</v>
       </c>
       <c r="G8" s="0">
@@ -1427,16 +1440,16 @@
       <c r="I8" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="0">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0">
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6">
         <v>0</v>
       </c>
       <c r="L8" s="0">
         <v>1</v>
       </c>
-      <c r="M8" s="0">
+      <c r="M8" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1447,16 +1460,16 @@
       <c r="B9" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="0">
+      <c r="C9" s="6">
         <v>50</v>
       </c>
       <c r="D9" s="0">
         <v>1</v>
       </c>
-      <c r="E9" s="0">
+      <c r="E9" s="6">
         <v>5</v>
       </c>
-      <c r="F9" s="0">
+      <c r="F9" s="6">
         <v>1</v>
       </c>
       <c r="G9" s="0">
@@ -1468,16 +1481,16 @@
       <c r="I9" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="0">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0">
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6">
         <v>0</v>
       </c>
       <c r="L9" s="0">
         <v>1</v>
       </c>
-      <c r="M9" s="0">
+      <c r="M9" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1488,16 +1501,16 @@
       <c r="B10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="0">
+      <c r="C10" s="6">
         <v>100</v>
       </c>
       <c r="D10" s="0">
         <v>2</v>
       </c>
-      <c r="E10" s="0">
+      <c r="E10" s="6">
         <v>10</v>
       </c>
-      <c r="F10" s="0">
+      <c r="F10" s="6">
         <v>1</v>
       </c>
       <c r="G10" s="0">
@@ -1509,16 +1522,16 @@
       <c r="I10" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="0">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0">
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
         <v>0</v>
       </c>
       <c r="L10" s="0">
         <v>1</v>
       </c>
-      <c r="M10" s="0">
+      <c r="M10" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1529,16 +1542,16 @@
       <c r="B11" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="0">
+      <c r="C11" s="6">
         <v>150</v>
       </c>
       <c r="D11" s="0">
         <v>3</v>
       </c>
-      <c r="E11" s="0">
+      <c r="E11" s="6">
         <v>20</v>
       </c>
-      <c r="F11" s="0">
+      <c r="F11" s="6">
         <v>1</v>
       </c>
       <c r="G11" s="0">
@@ -1550,16 +1563,16 @@
       <c r="I11" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="J11" s="0">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0">
+      <c r="J11" s="6">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6">
         <v>0</v>
       </c>
       <c r="L11" s="0">
         <v>1</v>
       </c>
-      <c r="M11" s="0">
+      <c r="M11" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1570,16 +1583,16 @@
       <c r="B12" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="0">
+      <c r="C12" s="6">
         <v>400</v>
       </c>
       <c r="D12" s="0">
         <v>1</v>
       </c>
-      <c r="E12" s="0">
-        <v>0</v>
-      </c>
-      <c r="F12" s="0">
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
         <v>0</v>
       </c>
       <c r="G12" s="0">
@@ -1591,16 +1604,16 @@
       <c r="I12" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="J12" s="0">
-        <v>0</v>
-      </c>
-      <c r="K12" s="0">
+      <c r="J12" s="6">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6">
         <v>0</v>
       </c>
       <c r="L12" s="0">
         <v>1</v>
       </c>
-      <c r="M12" s="0">
+      <c r="M12" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1611,16 +1624,16 @@
       <c r="B13" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="0">
+      <c r="C13" s="6">
         <v>800</v>
       </c>
       <c r="D13" s="0">
         <v>2</v>
       </c>
-      <c r="E13" s="0">
-        <v>0</v>
-      </c>
-      <c r="F13" s="0">
+      <c r="E13" s="6">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
         <v>0</v>
       </c>
       <c r="G13" s="0">
@@ -1632,16 +1645,16 @@
       <c r="I13" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="J13" s="0">
-        <v>0</v>
-      </c>
-      <c r="K13" s="0">
+      <c r="J13" s="6">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
         <v>0</v>
       </c>
       <c r="L13" s="0">
         <v>1</v>
       </c>
-      <c r="M13" s="0">
+      <c r="M13" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1652,16 +1665,16 @@
       <c r="B14" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="0">
+      <c r="C14" s="6">
         <v>1200</v>
       </c>
       <c r="D14" s="0">
         <v>3</v>
       </c>
-      <c r="E14" s="0">
-        <v>0</v>
-      </c>
-      <c r="F14" s="0">
+      <c r="E14" s="6">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
         <v>0</v>
       </c>
       <c r="G14" s="0">
@@ -1673,16 +1686,16 @@
       <c r="I14" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="J14" s="0">
-        <v>0</v>
-      </c>
-      <c r="K14" s="0">
+      <c r="J14" s="6">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6">
         <v>0</v>
       </c>
       <c r="L14" s="0">
         <v>1</v>
       </c>
-      <c r="M14" s="0">
+      <c r="M14" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1693,16 +1706,16 @@
       <c r="B15" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="0">
+      <c r="C15" s="6">
         <v>100</v>
       </c>
       <c r="D15" s="0">
         <v>1</v>
       </c>
-      <c r="E15" s="0">
+      <c r="E15" s="6">
         <v>30</v>
       </c>
-      <c r="F15" s="0">
+      <c r="F15" s="6">
         <v>1</v>
       </c>
       <c r="G15" s="0">
@@ -1714,16 +1727,16 @@
       <c r="I15" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="J15" s="0">
-        <v>0</v>
-      </c>
-      <c r="K15" s="0">
+      <c r="J15" s="6">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6">
         <v>0</v>
       </c>
       <c r="L15" s="0">
         <v>1</v>
       </c>
-      <c r="M15" s="0">
+      <c r="M15" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1734,16 +1747,16 @@
       <c r="B16" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C16" s="6">
         <v>150</v>
       </c>
       <c r="D16" s="0">
         <v>2</v>
       </c>
-      <c r="E16" s="0">
+      <c r="E16" s="6">
         <v>35</v>
       </c>
-      <c r="F16" s="0">
+      <c r="F16" s="6">
         <v>1</v>
       </c>
       <c r="G16" s="0">
@@ -1755,16 +1768,16 @@
       <c r="I16" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="J16" s="0">
-        <v>0</v>
-      </c>
-      <c r="K16" s="0">
+      <c r="J16" s="6">
+        <v>0</v>
+      </c>
+      <c r="K16" s="6">
         <v>0</v>
       </c>
       <c r="L16" s="0">
         <v>1</v>
       </c>
-      <c r="M16" s="0">
+      <c r="M16" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1775,16 +1788,16 @@
       <c r="B17" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="0">
+      <c r="C17" s="6">
         <v>200</v>
       </c>
       <c r="D17" s="0">
         <v>3</v>
       </c>
-      <c r="E17" s="0">
+      <c r="E17" s="6">
         <v>40</v>
       </c>
-      <c r="F17" s="0">
+      <c r="F17" s="6">
         <v>1</v>
       </c>
       <c r="G17" s="0">
@@ -1796,16 +1809,16 @@
       <c r="I17" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="J17" s="0">
-        <v>0</v>
-      </c>
-      <c r="K17" s="0">
+      <c r="J17" s="6">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6">
         <v>0</v>
       </c>
       <c r="L17" s="0">
         <v>1</v>
       </c>
-      <c r="M17" s="0">
+      <c r="M17" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1816,16 +1829,16 @@
       <c r="B18" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="0">
+      <c r="C18" s="6">
         <v>150</v>
       </c>
       <c r="D18" s="0">
         <v>1</v>
       </c>
-      <c r="E18" s="0">
+      <c r="E18" s="6">
         <v>50</v>
       </c>
-      <c r="F18" s="0">
+      <c r="F18" s="6">
         <v>1</v>
       </c>
       <c r="G18" s="0">
@@ -1837,16 +1850,16 @@
       <c r="I18" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="J18" s="0">
-        <v>0</v>
-      </c>
-      <c r="K18" s="0">
+      <c r="J18" s="6">
+        <v>0</v>
+      </c>
+      <c r="K18" s="6">
         <v>0</v>
       </c>
       <c r="L18" s="0">
         <v>1</v>
       </c>
-      <c r="M18" s="0">
+      <c r="M18" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1857,16 +1870,16 @@
       <c r="B19" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="0">
+      <c r="C19" s="6">
         <v>200</v>
       </c>
       <c r="D19" s="0">
         <v>2</v>
       </c>
-      <c r="E19" s="0">
+      <c r="E19" s="6">
         <v>55</v>
       </c>
-      <c r="F19" s="0">
+      <c r="F19" s="6">
         <v>1</v>
       </c>
       <c r="G19" s="0">
@@ -1878,16 +1891,16 @@
       <c r="I19" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="J19" s="0">
-        <v>0</v>
-      </c>
-      <c r="K19" s="0">
+      <c r="J19" s="6">
+        <v>0</v>
+      </c>
+      <c r="K19" s="6">
         <v>0</v>
       </c>
       <c r="L19" s="0">
         <v>1</v>
       </c>
-      <c r="M19" s="0">
+      <c r="M19" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1898,16 +1911,16 @@
       <c r="B20" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="0">
+      <c r="C20" s="6">
         <v>250</v>
       </c>
       <c r="D20" s="0">
         <v>3</v>
       </c>
-      <c r="E20" s="0">
+      <c r="E20" s="6">
         <v>60</v>
       </c>
-      <c r="F20" s="0">
+      <c r="F20" s="6">
         <v>1</v>
       </c>
       <c r="G20" s="0">
@@ -1919,16 +1932,16 @@
       <c r="I20" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="J20" s="0">
-        <v>0</v>
-      </c>
-      <c r="K20" s="0">
+      <c r="J20" s="6">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6">
         <v>0</v>
       </c>
       <c r="L20" s="0">
         <v>1</v>
       </c>
-      <c r="M20" s="0">
+      <c r="M20" s="6">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild="10.105.262.54977"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA90F6FF-4B36-4ABC-87A2-0CD77B8A2E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="TowerData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Health</t>
   </si>
@@ -128,82 +123,363 @@
   </si>
   <si>
     <t>nextlevelID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
+      <color theme="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="11"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F76"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F3F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="0"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -218,26 +494,270 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFACCCEA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399980"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -247,21 +767,57 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="49">
+    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
+    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
+    <cellStyle name="경고문" xfId="9" builtinId="11"/>
+    <cellStyle name="계산" xfId="17" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
+    <cellStyle name="메모" xfId="8" builtinId="10"/>
+    <cellStyle name="백분율" xfId="5" builtinId="5"/>
+    <cellStyle name="보통" xfId="23" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
+    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
     <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="20" builtinId="25"/>
+    <cellStyle name="입력" xfId="15" builtinId="20"/>
+    <cellStyle name="제목" xfId="10" builtinId="15"/>
+    <cellStyle name="제목 1" xfId="11" builtinId="16"/>
+    <cellStyle name="제목 2" xfId="12" builtinId="17"/>
+    <cellStyle name="제목 3" xfId="13" builtinId="18"/>
+    <cellStyle name="제목 4" xfId="14" builtinId="19"/>
+    <cellStyle name="좋음" xfId="21" builtinId="26"/>
+    <cellStyle name="출력" xfId="16" builtinId="21"/>
+    <cellStyle name="통화" xfId="4" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -549,28 +1105,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" style="3" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="3"/>
+    <col min="1" max="1" style="3" width="5.50500011" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" style="3" width="13.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="3" style="3" width="13.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" style="3" width="9.50500011" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" style="3" width="5.75500011" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="6" style="3" width="13.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="7" max="7" style="3" width="13.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="8" max="8" style="3" width="12.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="9" max="9" style="3" width="13.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="10" max="10" style="3" width="11.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="11" max="11" style="3" width="11.13000011" customWidth="1" outlineLevel="0"/>
+    <col min="12" max="12" style="3" width="14.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="13" max="13" style="3" width="12.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="14" max="14" style="3" width="13.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="15" max="16384" style="3" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -614,7 +1170,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
@@ -658,15 +1214,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="3">
-        <v>1002</v>
+        <v>2</v>
       </c>
       <c r="D3" s="4">
         <v>50</v>
@@ -702,15 +1258,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
-        <v>1002</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="3">
-        <v>1003</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4">
         <v>100</v>
@@ -746,9 +1302,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
-        <v>1003</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>12</v>
@@ -790,15 +1346,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
-        <v>1004</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="3">
-        <v>1005</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4">
         <v>50</v>
@@ -834,15 +1390,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
-        <v>1005</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="3">
-        <v>1006</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4">
         <v>100</v>
@@ -878,9 +1434,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
-        <v>1006</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>15</v>
@@ -922,15 +1478,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
-        <v>1007</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="3">
-        <v>1008</v>
+        <v>8</v>
       </c>
       <c r="D9" s="4">
         <v>50</v>
@@ -966,15 +1522,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
-        <v>1008</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="3">
-        <v>1009</v>
+        <v>9</v>
       </c>
       <c r="D10" s="4">
         <v>100</v>
@@ -1010,9 +1566,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
-        <v>1009</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>18</v>
@@ -1054,15 +1610,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="3">
-        <v>1011</v>
+        <v>11</v>
       </c>
       <c r="D12" s="4">
         <v>400</v>
@@ -1098,15 +1654,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
-        <v>1011</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="3">
-        <v>1012</v>
+        <v>12</v>
       </c>
       <c r="D13" s="4">
         <v>800</v>
@@ -1142,9 +1698,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
-        <v>1012</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>21</v>
@@ -1186,15 +1742,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
-        <v>1013</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C15" s="3">
-        <v>1014</v>
+        <v>14</v>
       </c>
       <c r="D15" s="4">
         <v>100</v>
@@ -1230,15 +1786,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
-        <v>1014</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="3">
-        <v>1015</v>
+        <v>15</v>
       </c>
       <c r="D16" s="4">
         <v>150</v>
@@ -1274,9 +1830,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
-        <v>1015</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
@@ -1318,15 +1874,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
-        <v>1016</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="3">
-        <v>1017</v>
+        <v>17</v>
       </c>
       <c r="D18" s="4">
         <v>150</v>
@@ -1362,15 +1918,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
-        <v>1017</v>
+        <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C19" s="3">
-        <v>1018</v>
+        <v>18</v>
       </c>
       <c r="D19" s="4">
         <v>200</v>
@@ -1406,9 +1962,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
-        <v>1018</v>
+        <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>27</v>
@@ -1452,7 +2008,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild="10.105.262.54977"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="36" windowWidth="25752" windowHeight="11592"/>
   </bookViews>
   <sheets>
     <sheet name="TowerData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
   <si>
     <t>Health</t>
   </si>
@@ -140,346 +144,60 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="10"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="11"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="11"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFF0000"/>
-    </font>
-    <font>
-      <sz val="18.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF3F3F76"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF3F3F3F"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFA7D00"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFA7D00"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="1"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF006100"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF9C0006"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF9C6500"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="0"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FF000000"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -494,270 +212,26 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FFACCCEA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399980"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -767,57 +241,21 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
-    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
-    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
-    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
-    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
-    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
-    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
-    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
-    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
-    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
-    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
-    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
-    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
-    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
-    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
-    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
-    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
-    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
-    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
-    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
-    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
-    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
-    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
-    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
-    <cellStyle name="경고문" xfId="9" builtinId="11"/>
-    <cellStyle name="계산" xfId="17" builtinId="22"/>
-    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
-    <cellStyle name="메모" xfId="8" builtinId="10"/>
-    <cellStyle name="백분율" xfId="5" builtinId="5"/>
-    <cellStyle name="보통" xfId="23" builtinId="28"/>
-    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
-    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
-    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
-    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
-    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
+  <cellStyles count="3">
     <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="요약" xfId="20" builtinId="25"/>
-    <cellStyle name="입력" xfId="15" builtinId="20"/>
-    <cellStyle name="제목" xfId="10" builtinId="15"/>
-    <cellStyle name="제목 1" xfId="11" builtinId="16"/>
-    <cellStyle name="제목 2" xfId="12" builtinId="17"/>
-    <cellStyle name="제목 3" xfId="13" builtinId="18"/>
-    <cellStyle name="제목 4" xfId="14" builtinId="19"/>
-    <cellStyle name="좋음" xfId="21" builtinId="26"/>
-    <cellStyle name="출력" xfId="16" builtinId="21"/>
-    <cellStyle name="통화" xfId="4" builtinId="4"/>
-    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1105,28 +543,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultRowHeight="16.500000"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" style="3" width="5.50500011" customWidth="1" outlineLevel="0"/>
-    <col min="2" max="2" style="3" width="13.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="3" max="3" style="3" width="13.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="4" max="4" style="3" width="9.50500011" customWidth="1" outlineLevel="0"/>
-    <col min="5" max="5" style="3" width="5.75500011" customWidth="1" outlineLevel="0"/>
-    <col min="6" max="6" style="3" width="13.25500011" customWidth="1" outlineLevel="0"/>
-    <col min="7" max="7" style="3" width="13.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="8" max="8" style="3" width="12.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="9" max="9" style="3" width="13.63000011" customWidth="1" outlineLevel="0"/>
-    <col min="10" max="10" style="3" width="11.63000011" customWidth="1" outlineLevel="0"/>
-    <col min="11" max="11" style="3" width="11.13000011" customWidth="1" outlineLevel="0"/>
-    <col min="12" max="12" style="3" width="14.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="13" max="13" style="3" width="12.63000011" customWidth="1" outlineLevel="0"/>
-    <col min="14" max="14" style="3" width="13.88000011" customWidth="1" outlineLevel="0"/>
-    <col min="15" max="16384" style="3" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="1" max="1" width="5.5" style="3" customWidth="1"/>
+    <col min="2" max="3" width="13" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.796875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.296875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.59765625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="11.59765625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11.09765625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14" style="3" customWidth="1"/>
+    <col min="13" max="13" width="12.59765625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="13.8984375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="9" style="3" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -1170,7 +608,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
@@ -1214,7 +652,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1258,7 +696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1302,7 +740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1346,7 +784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1378,10 +816,10 @@
         <v>31</v>
       </c>
       <c r="K6" s="4">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L6" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="3">
         <v>1</v>
@@ -1390,7 +828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1422,10 +860,10 @@
         <v>31</v>
       </c>
       <c r="K7" s="4">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L7" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="3">
         <v>1</v>
@@ -1434,7 +872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1466,10 +904,10 @@
         <v>31</v>
       </c>
       <c r="K8" s="4">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L8" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="3">
         <v>1</v>
@@ -1478,7 +916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1516,13 +954,13 @@
         <v>0</v>
       </c>
       <c r="M9" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N9" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1560,13 +998,13 @@
         <v>0</v>
       </c>
       <c r="M10" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N10" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1604,13 +1042,13 @@
         <v>0</v>
       </c>
       <c r="M11" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N11" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1654,7 +1092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1698,7 +1136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1742,7 +1180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1783,10 +1221,10 @@
         <v>1</v>
       </c>
       <c r="N15" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1827,10 +1265,10 @@
         <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1871,10 +1309,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1918,7 +1356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1962,7 +1400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -2008,7 +1446,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -1,25 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Polaris Office Sheet" lastEdited="6" lowestEdited="6" rupBuild="10.105.262.54977"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="36" windowWidth="25752" windowHeight="11592"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="TowerData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Health</t>
   </si>
@@ -139,65 +135,354 @@
   </si>
   <si>
     <t>Type</t>
+  </si>
+  <si>
+    <t>Prefab</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
+      <color theme="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="11"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F76"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F3F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="0"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -212,26 +497,270 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFACCCEA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399980"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -241,21 +770,57 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="49">
+    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
+    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
+    <cellStyle name="경고문" xfId="9" builtinId="11"/>
+    <cellStyle name="계산" xfId="17" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
+    <cellStyle name="메모" xfId="8" builtinId="10"/>
+    <cellStyle name="백분율" xfId="5" builtinId="5"/>
+    <cellStyle name="보통" xfId="23" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
+    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
     <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="20" builtinId="25"/>
+    <cellStyle name="입력" xfId="15" builtinId="20"/>
+    <cellStyle name="제목" xfId="10" builtinId="15"/>
+    <cellStyle name="제목 1" xfId="11" builtinId="16"/>
+    <cellStyle name="제목 2" xfId="12" builtinId="17"/>
+    <cellStyle name="제목 3" xfId="13" builtinId="18"/>
+    <cellStyle name="제목 4" xfId="14" builtinId="19"/>
+    <cellStyle name="좋음" xfId="21" builtinId="26"/>
+    <cellStyle name="출력" xfId="16" builtinId="21"/>
+    <cellStyle name="통화" xfId="4" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -543,28 +1108,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="3" customWidth="1"/>
-    <col min="2" max="3" width="13" style="3" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.796875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.296875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.59765625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="11.59765625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="11.09765625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="14" style="3" customWidth="1"/>
-    <col min="13" max="13" width="12.59765625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="13.8984375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="9" style="3" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="3"/>
+    <col min="1" max="1" style="3" width="5.50500011" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="3" style="3" width="13.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" style="3" width="9.50500011" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" style="3" width="5.75500011" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="6" style="3" width="13.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="7" max="7" style="3" width="13.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="8" max="8" style="3" width="12.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="9" max="9" style="3" width="13.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="10" max="10" style="3" width="11.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="11" max="11" style="3" width="11.13000011" customWidth="1" outlineLevel="0"/>
+    <col min="12" max="12" style="3" width="14.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="13" max="13" style="3" width="12.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="14" max="14" style="3" width="13.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="15" max="15" style="3" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="16" max="16384" style="3" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -607,8 +1172,11 @@
       <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
@@ -651,8 +1219,11 @@
       <c r="N2" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="O2" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -696,7 +1267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -740,7 +1311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -784,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -828,7 +1399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -872,7 +1443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -916,7 +1487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -960,7 +1531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1004,7 +1575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:15">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1048,7 +1619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:15">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1092,7 +1663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:15">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1136,7 +1707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:15">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1180,7 +1751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1224,7 +1795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:15">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1268,7 +1839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1312,7 +1883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1356,7 +1927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1400,7 +1971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1446,7 +2017,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris Office Sheet" lastEdited="6" lowestEdited="6" rupBuild="10.105.262.54977"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="36" windowWidth="25752" windowHeight="11592"/>
   </bookViews>
   <sheets>
     <sheet name="TowerData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
   <si>
     <t>Health</t>
   </si>
@@ -135,354 +139,65 @@
   </si>
   <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>Prefab</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="10"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="11"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="11"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFF0000"/>
-    </font>
-    <font>
-      <sz val="18.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF3F3F76"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF3F3F3F"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFA7D00"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFA7D00"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="1"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF006100"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF9C0006"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF9C6500"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="0"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FF000000"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -497,270 +212,26 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FFACCCEA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399980"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -770,57 +241,21 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
-    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
-    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
-    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
-    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
-    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
-    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
-    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
-    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
-    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
-    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
-    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
-    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
-    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
-    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
-    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
-    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
-    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
-    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
-    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
-    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
-    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
-    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
-    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
-    <cellStyle name="경고문" xfId="9" builtinId="11"/>
-    <cellStyle name="계산" xfId="17" builtinId="22"/>
-    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
-    <cellStyle name="메모" xfId="8" builtinId="10"/>
-    <cellStyle name="백분율" xfId="5" builtinId="5"/>
-    <cellStyle name="보통" xfId="23" builtinId="28"/>
-    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
-    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
-    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
-    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
-    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
+  <cellStyles count="3">
     <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="요약" xfId="20" builtinId="25"/>
-    <cellStyle name="입력" xfId="15" builtinId="20"/>
-    <cellStyle name="제목" xfId="10" builtinId="15"/>
-    <cellStyle name="제목 1" xfId="11" builtinId="16"/>
-    <cellStyle name="제목 2" xfId="12" builtinId="17"/>
-    <cellStyle name="제목 3" xfId="13" builtinId="18"/>
-    <cellStyle name="제목 4" xfId="14" builtinId="19"/>
-    <cellStyle name="좋음" xfId="21" builtinId="26"/>
-    <cellStyle name="출력" xfId="16" builtinId="21"/>
-    <cellStyle name="통화" xfId="4" builtinId="4"/>
-    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1108,28 +543,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="16.500000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" style="3" width="5.50500011" customWidth="1" outlineLevel="0"/>
-    <col min="2" max="3" style="3" width="13.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="4" max="4" style="3" width="9.50500011" customWidth="1" outlineLevel="0"/>
-    <col min="5" max="5" style="3" width="5.75500011" customWidth="1" outlineLevel="0"/>
-    <col min="6" max="6" style="3" width="13.25500011" customWidth="1" outlineLevel="0"/>
-    <col min="7" max="7" style="3" width="13.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="8" max="8" style="3" width="12.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="9" max="9" style="3" width="13.63000011" customWidth="1" outlineLevel="0"/>
-    <col min="10" max="10" style="3" width="11.63000011" customWidth="1" outlineLevel="0"/>
-    <col min="11" max="11" style="3" width="11.13000011" customWidth="1" outlineLevel="0"/>
-    <col min="12" max="12" style="3" width="14.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="13" max="13" style="3" width="12.63000011" customWidth="1" outlineLevel="0"/>
-    <col min="14" max="14" style="3" width="13.88000011" customWidth="1" outlineLevel="0"/>
-    <col min="15" max="15" style="3" width="9.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="16" max="16384" style="3" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="1" max="1" width="5.5" style="3" customWidth="1"/>
+    <col min="2" max="3" width="13" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.796875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.296875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.59765625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="11.59765625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11.09765625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14" style="3" customWidth="1"/>
+    <col min="13" max="13" width="12.59765625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="13.8984375" style="3" customWidth="1"/>
+    <col min="15" max="16" width="9" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -1172,11 +607,8 @@
       <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
@@ -1219,11 +651,8 @@
       <c r="N2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1234,7 +663,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
@@ -1267,7 +696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1278,13 +707,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="4">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="E4" s="3">
         <v>2</v>
       </c>
       <c r="F4" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G4" s="4">
         <v>1</v>
@@ -1311,7 +740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1322,13 +751,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="4">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3">
         <v>3</v>
       </c>
       <c r="F5" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G5" s="4">
         <v>1</v>
@@ -1355,7 +784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1378,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I6" s="3">
         <v>0</v>
@@ -1399,7 +828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1410,13 +839,13 @@
         <v>6</v>
       </c>
       <c r="D7" s="4">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="E7" s="3">
         <v>2</v>
       </c>
       <c r="F7" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G7" s="4">
         <v>1</v>
@@ -1425,7 +854,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>31</v>
@@ -1443,7 +872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1454,13 +883,13 @@
         <v>0</v>
       </c>
       <c r="D8" s="4">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3">
         <v>3</v>
       </c>
       <c r="F8" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G8" s="4">
         <v>1</v>
@@ -1469,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>31</v>
@@ -1487,7 +916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1498,19 +927,19 @@
         <v>8</v>
       </c>
       <c r="D9" s="4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E9" s="3">
         <v>1</v>
       </c>
       <c r="F9" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" s="4">
         <v>1</v>
       </c>
       <c r="H9" s="3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
@@ -1531,7 +960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1542,13 +971,13 @@
         <v>9</v>
       </c>
       <c r="D10" s="4">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E10" s="3">
         <v>2</v>
       </c>
       <c r="F10" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G10" s="4">
         <v>1</v>
@@ -1557,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>33</v>
@@ -1575,7 +1004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1586,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="D11" s="4">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="E11" s="3">
         <v>3</v>
       </c>
       <c r="F11" s="4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G11" s="4">
         <v>1</v>
@@ -1601,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>33</v>
@@ -1619,7 +1048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1663,7 +1092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1689,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>32</v>
@@ -1707,7 +1136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1751,7 +1180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1762,16 +1191,16 @@
         <v>14</v>
       </c>
       <c r="D15" s="4">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E15" s="3">
         <v>1</v>
       </c>
       <c r="F15" s="4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G15" s="4">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1792,10 +1221,10 @@
         <v>1</v>
       </c>
       <c r="N15" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1806,16 +1235,16 @@
         <v>15</v>
       </c>
       <c r="D16" s="4">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="E16" s="3">
         <v>2</v>
       </c>
       <c r="F16" s="4">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G16" s="4">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H16" s="3">
         <v>0</v>
@@ -1836,10 +1265,10 @@
         <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1850,16 +1279,16 @@
         <v>0</v>
       </c>
       <c r="D17" s="4">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="E17" s="3">
         <v>3</v>
       </c>
       <c r="F17" s="4">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G17" s="4">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H17" s="3">
         <v>0</v>
@@ -1880,10 +1309,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1894,16 +1323,16 @@
         <v>17</v>
       </c>
       <c r="D18" s="4">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="E18" s="3">
         <v>1</v>
       </c>
       <c r="F18" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G18" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="3">
         <v>120</v>
@@ -1927,7 +1356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1938,16 +1367,16 @@
         <v>18</v>
       </c>
       <c r="D19" s="4">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="E19" s="3">
         <v>2</v>
       </c>
       <c r="F19" s="4">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="G19" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="3">
         <v>0</v>
@@ -1971,7 +1400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1982,16 +1411,16 @@
         <v>0</v>
       </c>
       <c r="D20" s="4">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="E20" s="3">
         <v>3</v>
       </c>
       <c r="F20" s="4">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G20" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -2017,7 +1446,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1948E3FD-7369-4B39-AC5A-069C74F14DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="36" windowWidth="25752" windowHeight="11592"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TowerData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -144,7 +158,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
@@ -191,7 +205,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -214,6 +228,86 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -226,7 +320,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -237,7 +331,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -543,28 +670,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5" style="3" customWidth="1"/>
     <col min="2" max="3" width="13" style="3" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.796875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.296875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.75" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.25" style="3" customWidth="1"/>
     <col min="7" max="7" width="13" style="3" customWidth="1"/>
     <col min="8" max="8" width="12" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.59765625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="11.59765625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="11.09765625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="11.625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11.125" style="3" customWidth="1"/>
     <col min="12" max="12" width="14" style="3" customWidth="1"/>
-    <col min="13" max="13" width="12.59765625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="13.8984375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="12.625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="13.875" style="3" customWidth="1"/>
     <col min="15" max="16" width="9" style="3" customWidth="1"/>
     <col min="17" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -608,7 +735,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
@@ -652,795 +779,795 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A3" s="3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>2</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="6">
         <v>40</v>
       </c>
-      <c r="E3" s="3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4">
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6">
         <v>5</v>
       </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3">
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
         <v>20</v>
       </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="4">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>1</v>
-      </c>
-      <c r="N3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A4" s="3">
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="9">
         <v>3</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="10">
         <v>45</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="9">
         <v>2</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="10">
         <v>8</v>
       </c>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
+      <c r="G4" s="10">
+        <v>1</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0</v>
+      </c>
+      <c r="I4" s="9">
         <v>30</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="4">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>1</v>
-      </c>
-      <c r="N4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A5" s="3">
+      <c r="K4" s="10">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <v>1</v>
+      </c>
+      <c r="N4" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="12">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C5" s="13">
+        <v>0</v>
+      </c>
+      <c r="D5" s="14">
         <v>50</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="13">
         <v>3</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="14">
         <v>11</v>
       </c>
-      <c r="G5" s="4">
-        <v>1</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
+      <c r="G5" s="14">
+        <v>1</v>
+      </c>
+      <c r="H5" s="13">
+        <v>0</v>
+      </c>
+      <c r="I5" s="13">
         <v>40</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="4">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3">
-        <v>1</v>
-      </c>
-      <c r="N5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A6" s="3">
+      <c r="K5" s="14">
+        <v>0</v>
+      </c>
+      <c r="L5" s="14">
+        <v>0</v>
+      </c>
+      <c r="M5" s="13">
+        <v>1</v>
+      </c>
+      <c r="N5" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>5</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="6">
         <v>50</v>
       </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
         <v>5</v>
       </c>
-      <c r="G6" s="4">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3">
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
         <v>40</v>
       </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="6">
         <v>0.3</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="6">
         <v>2</v>
       </c>
-      <c r="M6" s="3">
-        <v>1</v>
-      </c>
-      <c r="N6" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A7" s="3">
+      <c r="M6" s="5">
+        <v>1</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="9">
         <v>6</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="10">
         <v>55</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="9">
         <v>2</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="10">
         <v>8</v>
       </c>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
+      <c r="G7" s="10">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9">
         <v>50</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="10">
         <v>0.3</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="10">
         <v>2</v>
       </c>
-      <c r="M7" s="3">
-        <v>1</v>
-      </c>
-      <c r="N7" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A8" s="3">
+      <c r="M7" s="9">
+        <v>1</v>
+      </c>
+      <c r="N7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="12">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C8" s="13">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14">
         <v>60</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="13">
         <v>3</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="14">
         <v>11</v>
       </c>
-      <c r="G8" s="4">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="G8" s="14">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13">
         <v>60</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="14">
         <v>0.3</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="14">
         <v>2</v>
       </c>
-      <c r="M8" s="3">
-        <v>1</v>
-      </c>
-      <c r="N8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A9" s="3">
+      <c r="M8" s="13">
+        <v>1</v>
+      </c>
+      <c r="N8" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>8</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="6">
         <v>60</v>
       </c>
-      <c r="E9" s="3">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6">
         <v>4</v>
       </c>
-      <c r="G9" s="4">
-        <v>1</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="G9" s="6">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
         <v>60</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="s">
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K9" s="4">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
         <v>5</v>
       </c>
-      <c r="N9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A10" s="3">
+      <c r="N9" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="9">
         <v>9</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="10">
         <v>65</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="9">
         <v>2</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="10">
         <v>6</v>
       </c>
-      <c r="G10" s="4">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="G10" s="10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
         <v>70</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K10" s="4">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="K10" s="10">
+        <v>0</v>
+      </c>
+      <c r="L10" s="10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
         <v>5</v>
       </c>
-      <c r="N10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A11" s="3">
+      <c r="N10" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="12">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="3">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="C11" s="13">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
         <v>70</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="13">
         <v>3</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="14">
         <v>8</v>
       </c>
-      <c r="G11" s="4">
-        <v>1</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3">
+      <c r="G11" s="14">
+        <v>1</v>
+      </c>
+      <c r="H11" s="13">
+        <v>0</v>
+      </c>
+      <c r="I11" s="13">
         <v>80</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="K11" s="4">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
+      <c r="K11" s="14">
+        <v>0</v>
+      </c>
+      <c r="L11" s="14">
+        <v>0</v>
+      </c>
+      <c r="M11" s="13">
         <v>5</v>
       </c>
-      <c r="N11" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A12" s="3">
+      <c r="N11" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
         <v>10</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>11</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="6">
         <v>400</v>
       </c>
-      <c r="E12" s="3">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
         <v>75</v>
       </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="s">
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K12" s="4">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1</v>
-      </c>
-      <c r="N12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A13" s="3">
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>1</v>
+      </c>
+      <c r="N12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
         <v>11</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="9">
         <v>12</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="10">
         <v>800</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="9">
         <v>2</v>
       </c>
-      <c r="F13" s="4">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
+      <c r="F13" s="10">
+        <v>0</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0</v>
+      </c>
+      <c r="I13" s="9">
         <v>85</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="4">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3">
-        <v>1</v>
-      </c>
-      <c r="N13" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A14" s="3">
+      <c r="K13" s="10">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9">
+        <v>1</v>
+      </c>
+      <c r="N13" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="12">
         <v>12</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="3">
-        <v>0</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="C14" s="13">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
         <v>1200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="13">
         <v>3</v>
       </c>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
         <v>95</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K14" s="4">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>1</v>
-      </c>
-      <c r="N14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A15" s="3">
+      <c r="K14" s="14">
+        <v>0</v>
+      </c>
+      <c r="L14" s="14">
+        <v>0</v>
+      </c>
+      <c r="M14" s="13">
+        <v>1</v>
+      </c>
+      <c r="N14" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
         <v>13</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>14</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="6">
         <v>70</v>
       </c>
-      <c r="E15" s="3">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4">
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6">
         <v>15</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="6">
         <v>1.5</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="5">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="s">
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="K15" s="4">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>1</v>
-      </c>
-      <c r="N15" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A16" s="3">
+      <c r="K15" s="6">
+        <v>0</v>
+      </c>
+      <c r="L15" s="6">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>1</v>
+      </c>
+      <c r="N15" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
         <v>14</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="9">
         <v>15</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="10">
         <v>75</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="9">
         <v>2</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="10">
         <v>19</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="10">
         <v>1.5</v>
       </c>
-      <c r="H16" s="3">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3">
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
         <v>110</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K16" s="4">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
-        <v>1</v>
-      </c>
-      <c r="N16" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A17" s="3">
+      <c r="K16" s="10">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>1</v>
+      </c>
+      <c r="N16" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="12">
         <v>15</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="3">
-        <v>0</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="C17" s="13">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
         <v>80</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="13">
         <v>3</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="14">
         <v>23</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="14">
         <v>1.5</v>
       </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="H17" s="13">
+        <v>0</v>
+      </c>
+      <c r="I17" s="13">
         <v>120</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="J17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="K17" s="4">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1</v>
-      </c>
-      <c r="N17" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A18" s="3">
+      <c r="K17" s="14">
+        <v>0</v>
+      </c>
+      <c r="L17" s="14">
+        <v>0</v>
+      </c>
+      <c r="M17" s="13">
+        <v>1</v>
+      </c>
+      <c r="N17" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
         <v>16</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>17</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="6">
         <v>80</v>
       </c>
-      <c r="E18" s="3">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4">
+      <c r="E18" s="5">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6">
         <v>25</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="6">
         <v>2</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="5">
         <v>120</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="s">
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K18" s="4">
-        <v>0</v>
-      </c>
-      <c r="L18" s="4">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <v>1</v>
-      </c>
-      <c r="N18" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A19" s="3">
+      <c r="K18" s="6">
+        <v>0</v>
+      </c>
+      <c r="L18" s="6">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5">
+        <v>1</v>
+      </c>
+      <c r="N18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="9">
         <v>18</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="10">
         <v>85</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="9">
         <v>2</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="10">
         <v>35</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="10">
         <v>2</v>
       </c>
-      <c r="H19" s="3">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
+      <c r="H19" s="9">
+        <v>0</v>
+      </c>
+      <c r="I19" s="9">
         <v>130</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="J19" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="4">
-        <v>0</v>
-      </c>
-      <c r="L19" s="4">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3">
-        <v>1</v>
-      </c>
-      <c r="N19" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A20" s="3">
+      <c r="K19" s="10">
+        <v>0</v>
+      </c>
+      <c r="L19" s="10">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9">
+        <v>1</v>
+      </c>
+      <c r="N19" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="12">
         <v>18</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="3">
-        <v>0</v>
-      </c>
-      <c r="D20" s="4">
+      <c r="C20" s="13">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
         <v>90</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="13">
         <v>3</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="14">
         <v>45</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="14">
         <v>2</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="H20" s="13">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13">
         <v>140</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K20" s="4">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1</v>
-      </c>
-      <c r="N20" s="4">
+      <c r="K20" s="14">
+        <v>0</v>
+      </c>
+      <c r="L20" s="14">
+        <v>0</v>
+      </c>
+      <c r="M20" s="13">
+        <v>1</v>
+      </c>
+      <c r="N20" s="15">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1948E3FD-7369-4B39-AC5A-069C74F14DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E2C973-7A00-486C-AAFC-B0EBDFBEBA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -320,7 +320,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -346,10 +346,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -790,7 +787,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="6">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E3" s="5">
         <v>1</v>
@@ -827,87 +824,87 @@
       <c r="A4" s="8">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="3">
         <v>3</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>45</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="3">
         <v>2</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>8</v>
       </c>
-      <c r="G4" s="10">
-        <v>1</v>
-      </c>
-      <c r="H4" s="9">
-        <v>0</v>
-      </c>
-      <c r="I4" s="9">
+      <c r="G4" s="9">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
         <v>30</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="10">
-        <v>0</v>
-      </c>
-      <c r="L4" s="10">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9">
-        <v>1</v>
-      </c>
-      <c r="N4" s="11">
+      <c r="K4" s="9">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <v>1</v>
+      </c>
+      <c r="N4" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="12">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="13">
-        <v>0</v>
-      </c>
-      <c r="D5" s="14">
+      <c r="C5" s="12">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13">
         <v>50</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <v>3</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <v>11</v>
       </c>
-      <c r="G5" s="14">
-        <v>1</v>
-      </c>
-      <c r="H5" s="13">
-        <v>0</v>
-      </c>
-      <c r="I5" s="13">
+      <c r="G5" s="13">
+        <v>1</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0</v>
+      </c>
+      <c r="I5" s="12">
         <v>40</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="14">
-        <v>0</v>
-      </c>
-      <c r="L5" s="14">
-        <v>0</v>
-      </c>
-      <c r="M5" s="13">
-        <v>1</v>
-      </c>
-      <c r="N5" s="15">
+      <c r="K5" s="13">
+        <v>0</v>
+      </c>
+      <c r="L5" s="13">
+        <v>0</v>
+      </c>
+      <c r="M5" s="12">
+        <v>1</v>
+      </c>
+      <c r="N5" s="14">
         <v>0</v>
       </c>
     </row>
@@ -959,87 +956,87 @@
       <c r="A7" s="8">
         <v>5</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="3">
         <v>6</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>55</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="3">
         <v>2</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <v>8</v>
       </c>
-      <c r="G7" s="10">
-        <v>1</v>
-      </c>
-      <c r="H7" s="9">
-        <v>0</v>
-      </c>
-      <c r="I7" s="9">
+      <c r="G7" s="9">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
         <v>50</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="9">
         <v>0.3</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="9">
         <v>2</v>
       </c>
-      <c r="M7" s="9">
-        <v>1</v>
-      </c>
-      <c r="N7" s="11">
+      <c r="M7" s="3">
+        <v>1</v>
+      </c>
+      <c r="N7" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>6</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="13">
-        <v>0</v>
-      </c>
-      <c r="D8" s="14">
+      <c r="C8" s="12">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13">
         <v>60</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <v>3</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="13">
         <v>11</v>
       </c>
-      <c r="G8" s="14">
-        <v>1</v>
-      </c>
-      <c r="H8" s="13">
-        <v>0</v>
-      </c>
-      <c r="I8" s="13">
+      <c r="G8" s="13">
+        <v>1</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12">
         <v>60</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>0.3</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="13">
         <v>2</v>
       </c>
-      <c r="M8" s="13">
-        <v>1</v>
-      </c>
-      <c r="N8" s="15">
+      <c r="M8" s="12">
+        <v>1</v>
+      </c>
+      <c r="N8" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1091,87 +1088,87 @@
       <c r="A10" s="8">
         <v>8</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="3">
         <v>9</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>65</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="3">
         <v>2</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>6</v>
       </c>
-      <c r="G10" s="10">
-        <v>1</v>
-      </c>
-      <c r="H10" s="9">
-        <v>0</v>
-      </c>
-      <c r="I10" s="9">
+      <c r="G10" s="9">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
         <v>70</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K10" s="10">
-        <v>0</v>
-      </c>
-      <c r="L10" s="10">
-        <v>0</v>
-      </c>
-      <c r="M10" s="9">
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
         <v>5</v>
       </c>
-      <c r="N10" s="11">
+      <c r="N10" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="12">
+      <c r="A11" s="11">
         <v>9</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="13">
-        <v>0</v>
-      </c>
-      <c r="D11" s="14">
+      <c r="C11" s="12">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13">
         <v>70</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <v>3</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="13">
         <v>8</v>
       </c>
-      <c r="G11" s="14">
-        <v>1</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0</v>
-      </c>
-      <c r="I11" s="13">
+      <c r="G11" s="13">
+        <v>1</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0</v>
+      </c>
+      <c r="I11" s="12">
         <v>80</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="K11" s="14">
-        <v>0</v>
-      </c>
-      <c r="L11" s="14">
-        <v>0</v>
-      </c>
-      <c r="M11" s="13">
+      <c r="K11" s="13">
+        <v>0</v>
+      </c>
+      <c r="L11" s="13">
+        <v>0</v>
+      </c>
+      <c r="M11" s="12">
         <v>5</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1223,87 +1220,87 @@
       <c r="A13" s="8">
         <v>11</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="3">
         <v>12</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>800</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="3">
         <v>2</v>
       </c>
-      <c r="F13" s="10">
-        <v>0</v>
-      </c>
-      <c r="G13" s="10">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9">
-        <v>0</v>
-      </c>
-      <c r="I13" s="9">
+      <c r="F13" s="9">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
         <v>85</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="10">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9">
-        <v>1</v>
-      </c>
-      <c r="N13" s="11">
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>1</v>
+      </c>
+      <c r="N13" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="12">
+      <c r="A14" s="11">
         <v>12</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="13">
-        <v>0</v>
-      </c>
-      <c r="D14" s="14">
+      <c r="C14" s="12">
+        <v>0</v>
+      </c>
+      <c r="D14" s="13">
         <v>1200</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="12">
         <v>3</v>
       </c>
-      <c r="F14" s="14">
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13">
-        <v>0</v>
-      </c>
-      <c r="I14" s="13">
+      <c r="F14" s="13">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12">
+        <v>0</v>
+      </c>
+      <c r="I14" s="12">
         <v>95</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="K14" s="14">
-        <v>0</v>
-      </c>
-      <c r="L14" s="14">
-        <v>0</v>
-      </c>
-      <c r="M14" s="13">
-        <v>1</v>
-      </c>
-      <c r="N14" s="15">
+      <c r="K14" s="13">
+        <v>0</v>
+      </c>
+      <c r="L14" s="13">
+        <v>0</v>
+      </c>
+      <c r="M14" s="12">
+        <v>1</v>
+      </c>
+      <c r="N14" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1355,87 +1352,87 @@
       <c r="A16" s="8">
         <v>14</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="3">
         <v>15</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>75</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="3">
         <v>2</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <v>19</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="9">
         <v>1.5</v>
       </c>
-      <c r="H16" s="9">
-        <v>0</v>
-      </c>
-      <c r="I16" s="9">
+      <c r="H16" s="3">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
         <v>110</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="K16" s="10">
-        <v>0</v>
-      </c>
-      <c r="L16" s="10">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9">
-        <v>1</v>
-      </c>
-      <c r="N16" s="11">
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <v>1</v>
+      </c>
+      <c r="N16" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="12">
+      <c r="A17" s="11">
         <v>15</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13">
-        <v>0</v>
-      </c>
-      <c r="D17" s="14">
+      <c r="C17" s="12">
+        <v>0</v>
+      </c>
+      <c r="D17" s="13">
         <v>80</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="12">
         <v>3</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="13">
         <v>23</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="13">
         <v>1.5</v>
       </c>
-      <c r="H17" s="13">
-        <v>0</v>
-      </c>
-      <c r="I17" s="13">
+      <c r="H17" s="12">
+        <v>0</v>
+      </c>
+      <c r="I17" s="12">
         <v>120</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="K17" s="14">
-        <v>0</v>
-      </c>
-      <c r="L17" s="14">
-        <v>0</v>
-      </c>
-      <c r="M17" s="13">
-        <v>1</v>
-      </c>
-      <c r="N17" s="15">
+      <c r="K17" s="13">
+        <v>0</v>
+      </c>
+      <c r="L17" s="13">
+        <v>0</v>
+      </c>
+      <c r="M17" s="12">
+        <v>1</v>
+      </c>
+      <c r="N17" s="14">
         <v>1</v>
       </c>
     </row>
@@ -1487,87 +1484,87 @@
       <c r="A19" s="8">
         <v>17</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="3">
         <v>18</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>85</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="3">
         <v>2</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <v>35</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <v>2</v>
       </c>
-      <c r="H19" s="9">
-        <v>0</v>
-      </c>
-      <c r="I19" s="9">
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
         <v>130</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="10">
-        <v>0</v>
-      </c>
-      <c r="L19" s="10">
-        <v>0</v>
-      </c>
-      <c r="M19" s="9">
-        <v>1</v>
-      </c>
-      <c r="N19" s="11">
+      <c r="K19" s="9">
+        <v>0</v>
+      </c>
+      <c r="L19" s="9">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <v>1</v>
+      </c>
+      <c r="N19" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="12">
+      <c r="A20" s="11">
         <v>18</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13">
-        <v>0</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="12">
+        <v>0</v>
+      </c>
+      <c r="D20" s="13">
         <v>90</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="12">
         <v>3</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="13">
         <v>45</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="13">
         <v>2</v>
       </c>
-      <c r="H20" s="13">
-        <v>0</v>
-      </c>
-      <c r="I20" s="13">
+      <c r="H20" s="12">
+        <v>0</v>
+      </c>
+      <c r="I20" s="12">
         <v>140</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="K20" s="14">
-        <v>0</v>
-      </c>
-      <c r="L20" s="14">
-        <v>0</v>
-      </c>
-      <c r="M20" s="13">
-        <v>1</v>
-      </c>
-      <c r="N20" s="15">
+      <c r="K20" s="13">
+        <v>0</v>
+      </c>
+      <c r="L20" s="13">
+        <v>0</v>
+      </c>
+      <c r="M20" s="12">
+        <v>1</v>
+      </c>
+      <c r="N20" s="14">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excels/unit data.xlsx
+++ b/Assets/Excels/unit data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E2C973-7A00-486C-AAFC-B0EBDFBEBA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC296DCB-C03A-4916-B28D-DABF485C4168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -787,7 +787,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="6">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" s="5">
         <v>1</v>
@@ -831,7 +831,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="9">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
         <v>2</v>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="13">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E5" s="12">
         <v>3</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G9" s="6">
         <v>1</v>
@@ -1101,7 +1101,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="9">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G10" s="9">
         <v>1</v>
@@ -1145,7 +1145,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="13">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G11" s="13">
         <v>1</v>
@@ -1227,7 +1227,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="9">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E13" s="3">
         <v>2</v>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="13">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="E14" s="12">
         <v>3</v>
